--- a/input/timetable/Экономическая безопасность.xlsx
+++ b/input/timetable/Экономическая безопасность.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="124">
   <si>
     <t>пара</t>
   </si>
@@ -330,18 +330,9 @@
     <t>Иностр. язык в проф. сфере, п/г 1, К517//</t>
   </si>
   <si>
-    <t>//Иностр. язык в проф. сфере, п/г 2, К517//</t>
-  </si>
-  <si>
     <t>Анализ финансовой отчетности (пр), К603</t>
   </si>
   <si>
-    <t>Контроль и ревизия (лек), К428//</t>
-  </si>
-  <si>
-    <t>Контроль и ревизия (пр), К428</t>
-  </si>
-  <si>
     <t>// Анализ финансовой отчетности (лек), К613</t>
   </si>
   <si>
@@ -384,9 +375,6 @@
     <t>Экономическая теория (пр), К429//</t>
   </si>
   <si>
-    <t>Психология инклюзивного общества (пр), ЭОиДОТ//</t>
-  </si>
-  <si>
     <t>Анализ бухгалтерской отчетности (лек), К429</t>
   </si>
   <si>
@@ -400,6 +388,18 @@
   </si>
   <si>
     <t>Эконометрика (пр), К612</t>
+  </si>
+  <si>
+    <t>Контроль и ревизия (лек)/(пр), К508</t>
+  </si>
+  <si>
+    <t>Контроль и ревизия (пр), К508//</t>
+  </si>
+  <si>
+    <t>//Иностр. язык в проф. сфере, п/г 2, К517</t>
+  </si>
+  <si>
+    <t>// Психология инклюзивного общества (пр), К604</t>
   </si>
 </sst>
 </file>
@@ -1811,6 +1811,15 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1829,13 +1838,13 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1850,15 +1859,6 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2376,7 +2376,7 @@
         <v>4</v>
       </c>
       <c r="C12" s="95" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D12" s="96"/>
       <c r="E12" s="96"/>
@@ -2400,7 +2400,7 @@
         <v>6</v>
       </c>
       <c r="C14" s="86" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D14" s="87"/>
       <c r="E14" s="87"/>
@@ -2582,7 +2582,7 @@
         <v>5</v>
       </c>
       <c r="C29" s="80" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D29" s="81"/>
       <c r="E29" s="81"/>
@@ -2594,7 +2594,7 @@
         <v>6</v>
       </c>
       <c r="C30" s="80" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D30" s="81"/>
       <c r="E30" s="81"/>
@@ -2972,7 +2972,7 @@
         <v>7</v>
       </c>
       <c r="C14" s="135" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D14" s="136"/>
       <c r="E14" s="136"/>
@@ -3497,9 +3497,7 @@
       <c r="B11" s="45">
         <v>1</v>
       </c>
-      <c r="C11" s="155" t="s">
-        <v>118</v>
-      </c>
+      <c r="C11" s="155"/>
       <c r="D11" s="156"/>
       <c r="E11" s="156"/>
       <c r="F11" s="157"/>
@@ -3580,10 +3578,12 @@
       <c r="B18" s="21">
         <v>6</v>
       </c>
-      <c r="C18" s="101"/>
-      <c r="D18" s="102"/>
-      <c r="E18" s="102"/>
-      <c r="F18" s="103"/>
+      <c r="C18" s="126" t="s">
+        <v>123</v>
+      </c>
+      <c r="D18" s="127"/>
+      <c r="E18" s="127"/>
+      <c r="F18" s="128"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A19" s="16" t="s">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="D11" s="230"/>
       <c r="E11" s="230" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="F11" s="231"/>
     </row>
@@ -4075,7 +4075,7 @@
         <v>5</v>
       </c>
       <c r="C14" s="226" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D14" s="227"/>
       <c r="E14" s="227"/>
@@ -4098,36 +4098,32 @@
       <c r="B16" s="19">
         <v>2</v>
       </c>
-      <c r="C16" s="214" t="s">
-        <v>102</v>
-      </c>
-      <c r="D16" s="215"/>
-      <c r="E16" s="215"/>
-      <c r="F16" s="216"/>
+      <c r="C16" s="217"/>
+      <c r="D16" s="218"/>
+      <c r="E16" s="218"/>
+      <c r="F16" s="219"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A17" s="18"/>
       <c r="B17" s="19">
         <v>3</v>
       </c>
-      <c r="C17" s="217" t="s">
-        <v>103</v>
-      </c>
-      <c r="D17" s="218"/>
-      <c r="E17" s="218"/>
-      <c r="F17" s="219"/>
+      <c r="C17" s="220"/>
+      <c r="D17" s="221"/>
+      <c r="E17" s="221"/>
+      <c r="F17" s="222"/>
     </row>
     <row r="18" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="18"/>
       <c r="B18" s="19">
         <v>4</v>
       </c>
-      <c r="C18" s="220" t="s">
-        <v>104</v>
-      </c>
-      <c r="D18" s="221"/>
-      <c r="E18" s="221"/>
-      <c r="F18" s="222"/>
+      <c r="C18" s="214" t="s">
+        <v>101</v>
+      </c>
+      <c r="D18" s="215"/>
+      <c r="E18" s="215"/>
+      <c r="F18" s="216"/>
     </row>
     <row r="19" spans="1:6" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A19" s="24"/>
@@ -4147,7 +4143,7 @@
         <v>3</v>
       </c>
       <c r="C20" s="77" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D20" s="78"/>
       <c r="E20" s="78"/>
@@ -4159,7 +4155,7 @@
         <v>4</v>
       </c>
       <c r="C21" s="107" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D21" s="108"/>
       <c r="E21" s="108"/>
@@ -4171,7 +4167,7 @@
         <v>5</v>
       </c>
       <c r="C22" s="107" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D22" s="108"/>
       <c r="E22" s="108"/>
@@ -4194,12 +4190,10 @@
       <c r="B24" s="17">
         <v>1</v>
       </c>
-      <c r="C24" s="208" t="s">
-        <v>33</v>
-      </c>
-      <c r="D24" s="209"/>
-      <c r="E24" s="209"/>
-      <c r="F24" s="210"/>
+      <c r="C24" s="211"/>
+      <c r="D24" s="212"/>
+      <c r="E24" s="212"/>
+      <c r="F24" s="213"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A25" s="18"/>
@@ -4216,20 +4210,24 @@
       <c r="B26" s="19">
         <v>3</v>
       </c>
-      <c r="C26" s="211"/>
-      <c r="D26" s="212"/>
-      <c r="E26" s="212"/>
-      <c r="F26" s="213"/>
+      <c r="C26" s="214" t="s">
+        <v>120</v>
+      </c>
+      <c r="D26" s="215"/>
+      <c r="E26" s="215"/>
+      <c r="F26" s="216"/>
     </row>
     <row r="27" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A27" s="24"/>
       <c r="B27" s="21">
         <v>4</v>
       </c>
-      <c r="C27" s="194"/>
-      <c r="D27" s="195"/>
-      <c r="E27" s="195"/>
-      <c r="F27" s="196"/>
+      <c r="C27" s="205" t="s">
+        <v>121</v>
+      </c>
+      <c r="D27" s="206"/>
+      <c r="E27" s="206"/>
+      <c r="F27" s="207"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A28" s="16" t="s">
@@ -4239,7 +4237,7 @@
         <v>2</v>
       </c>
       <c r="C28" s="178" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D28" s="179"/>
       <c r="E28" s="179"/>
@@ -4251,7 +4249,7 @@
         <v>3</v>
       </c>
       <c r="C29" s="107" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D29" s="108"/>
       <c r="E29" s="108"/>
@@ -4262,10 +4260,10 @@
       <c r="B30" s="19">
         <v>4</v>
       </c>
-      <c r="C30" s="205"/>
-      <c r="D30" s="206"/>
-      <c r="E30" s="206"/>
-      <c r="F30" s="207"/>
+      <c r="C30" s="208"/>
+      <c r="D30" s="209"/>
+      <c r="E30" s="209"/>
+      <c r="F30" s="210"/>
     </row>
     <row r="31" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A31" s="46"/>
@@ -4284,12 +4282,12 @@
       <c r="B32" s="45">
         <v>2</v>
       </c>
-      <c r="C32" s="208" t="s">
-        <v>110</v>
-      </c>
-      <c r="D32" s="209"/>
-      <c r="E32" s="209"/>
-      <c r="F32" s="210"/>
+      <c r="C32" s="211" t="s">
+        <v>107</v>
+      </c>
+      <c r="D32" s="212"/>
+      <c r="E32" s="212"/>
+      <c r="F32" s="213"/>
     </row>
     <row r="33" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="28"/>
@@ -4297,7 +4295,7 @@
         <v>3</v>
       </c>
       <c r="C33" s="80" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D33" s="81"/>
       <c r="E33" s="81"/>
@@ -4571,7 +4569,7 @@
         <v>2</v>
       </c>
       <c r="C12" s="80" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D12" s="81"/>
       <c r="E12" s="81"/>
@@ -4583,7 +4581,7 @@
         <v>3</v>
       </c>
       <c r="C13" s="116" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D13" s="117"/>
       <c r="E13" s="117"/>
@@ -4671,7 +4669,7 @@
         <v>4</v>
       </c>
       <c r="C21" s="80" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D21" s="81"/>
       <c r="E21" s="81"/>
@@ -4683,7 +4681,7 @@
         <v>5</v>
       </c>
       <c r="C22" s="163" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D22" s="164"/>
       <c r="E22" s="164"/>
@@ -4717,7 +4715,7 @@
         <v>4</v>
       </c>
       <c r="C25" s="80" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D25" s="81"/>
       <c r="E25" s="81"/>
@@ -4729,7 +4727,7 @@
         <v>5</v>
       </c>
       <c r="C26" s="163" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D26" s="164"/>
       <c r="E26" s="164"/>

--- a/input/timetable/Экономическая безопасность.xlsx
+++ b/input/timetable/Экономическая безопасность.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13605" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13605" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="1 курс" sheetId="26" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="163">
   <si>
     <t>пара</t>
   </si>
@@ -75,6 +75,9 @@
     <t>Зав. кафедрой</t>
   </si>
   <si>
+    <t>Преподаватель</t>
+  </si>
+  <si>
     <t>экономики и управления</t>
   </si>
   <si>
@@ -135,13 +138,46 @@
     <t>ТО</t>
   </si>
   <si>
+    <t>Ахтемзянова Н.М.</t>
+  </si>
+  <si>
     <t>Русский язык и культура речи (лек 32ч)</t>
   </si>
   <si>
+    <t>Хадынская А.А.</t>
+  </si>
+  <si>
+    <t>Прокопьев А.В.</t>
+  </si>
+  <si>
+    <t>Минникова Ю.М.</t>
+  </si>
+  <si>
     <t>Физическая культура и спорт (лек 8ч)</t>
   </si>
   <si>
+    <t>Латыпова Э.А.</t>
+  </si>
+  <si>
+    <t>Тимофеева Н.В.</t>
+  </si>
+  <si>
+    <t>Прокопьева Т.В.</t>
+  </si>
+  <si>
+    <t>Ямпольская Н.Ю.</t>
+  </si>
+  <si>
     <t>406-31</t>
+  </si>
+  <si>
+    <t>Лешукова Е.В.</t>
+  </si>
+  <si>
+    <t>Дорожкина Е.В.</t>
+  </si>
+  <si>
+    <t>Трухина О.А.</t>
   </si>
   <si>
     <t>Философия (лекция 32 ч)</t>
@@ -153,6 +189,15 @@
 </t>
   </si>
   <si>
+    <t>Минникова Ю.М</t>
+  </si>
+  <si>
+    <t>Мартиросян Л.А.</t>
+  </si>
+  <si>
+    <t>Шутро Е.Н.</t>
+  </si>
+  <si>
     <t>Бухгалтерский учет (пр), К612</t>
   </si>
   <si>
@@ -168,12 +213,27 @@
     <t>Цифровая грамотность (лек 16 ч)</t>
   </si>
   <si>
+    <t>Мойсеенкова М.А.</t>
+  </si>
+  <si>
+    <t>Подлуцкая К.А.; Литовченко А.С.</t>
+  </si>
+  <si>
     <t>Экономика организации (предприятия) (лек), К613</t>
   </si>
   <si>
     <t>Экономика организации (предприятия) (пр), К613</t>
   </si>
   <si>
+    <t>Осипова А.В.</t>
+  </si>
+  <si>
+    <t>Минникова Ю.М.;Литовченко А.С.</t>
+  </si>
+  <si>
+    <t>Мкртчян Л.Л.</t>
+  </si>
+  <si>
     <t>Эконометрика (лек), К612/ /Информационные технологии в экономике (лек), К612</t>
   </si>
   <si>
@@ -198,15 +258,30 @@
     <t>Элект. дисциплины по физич. культуре и спорту проводятся  1 парой или  2 парой в зависимости от выбранной элективной дисциплины., занятия в объеме 16 часов провдятся по отдельному расписанию.</t>
   </si>
   <si>
+    <t>Усаева Н.Р.</t>
+  </si>
+  <si>
     <t>Психология инклюзивного общества (лекция 16 ч)</t>
   </si>
   <si>
+    <t>Малагин Д.В.</t>
+  </si>
+  <si>
+    <t>Исаева И.А.</t>
+  </si>
+  <si>
+    <t>Шарамеева О.А.</t>
+  </si>
+  <si>
     <t>Управленческий учет (лек), К613</t>
   </si>
   <si>
     <t>Управленческий учет (пр), К613</t>
   </si>
   <si>
+    <t>Усольцев Ю.М.</t>
+  </si>
+  <si>
     <t>Бухгалтерский учет (лек). К613</t>
   </si>
   <si>
@@ -234,6 +309,15 @@
     <t>02.02.2026-07.04.2026</t>
   </si>
   <si>
+    <t>Андрейченко А.И.</t>
+  </si>
+  <si>
+    <t>Галлямова Л.В.</t>
+  </si>
+  <si>
+    <t>Данаев А.М.</t>
+  </si>
+  <si>
     <t>Финансы (пр), К612</t>
   </si>
   <si>
@@ -258,6 +342,12 @@
     <t>ФТД: Цифровая грамотность (пр), К433</t>
   </si>
   <si>
+    <t>Бутенко Н.А.</t>
+  </si>
+  <si>
+    <t>Калинина Е.А.</t>
+  </si>
+  <si>
     <t>Основы проектной деятельности (лекция 16 ч)</t>
   </si>
   <si>
@@ -267,18 +357,30 @@
     <t>Экономическая безопасность государства (пр), К612</t>
   </si>
   <si>
+    <t>Каратаев А.С</t>
+  </si>
+  <si>
     <t>Работа в команде (пр), К612//</t>
   </si>
   <si>
     <t>Экономический анализ (пр), К612</t>
   </si>
   <si>
+    <t>Подлуцкая К.А.</t>
+  </si>
+  <si>
     <t>Иностранный язык, п/г 1, К314</t>
   </si>
   <si>
     <t>Философия (пр). К412//</t>
   </si>
   <si>
+    <t>Фейзуллаев М.А.</t>
+  </si>
+  <si>
+    <t>Макаренко И.В.</t>
+  </si>
+  <si>
     <t>Иностранный язык в проф. сфере (24 ч), п/г 1, К413</t>
   </si>
   <si>
@@ -327,6 +429,12 @@
     <t>Аудит (лек), К612</t>
   </si>
   <si>
+    <t>Емонакова Н.А.</t>
+  </si>
+  <si>
+    <t>Шайдуров А.В.</t>
+  </si>
+  <si>
     <t>Иностр. язык в проф. сфере, п/г 1, К517//</t>
   </si>
   <si>
@@ -357,6 +465,9 @@
     <t>Корпоративное право (пр), К612</t>
   </si>
   <si>
+    <t>Каратаев А.С.</t>
+  </si>
+  <si>
     <t>Анализ внешнеэкономической деятельности  (лек), К613</t>
   </si>
   <si>
@@ -387,6 +498,9 @@
     <t>Финансы (лек), К613//</t>
   </si>
   <si>
+    <t>Киященко Т.П.</t>
+  </si>
+  <si>
     <t>Эконометрика (пр), К612</t>
   </si>
   <si>
@@ -400,6 +514,9 @@
   </si>
   <si>
     <t>// Психология инклюзивного общества (пр), К604</t>
+  </si>
+  <si>
+    <t>Батыршина К.Г.</t>
   </si>
 </sst>
 </file>
@@ -519,7 +636,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -538,6 +655,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -549,7 +672,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="61">
+  <borders count="65">
     <border>
       <left/>
       <right/>
@@ -681,6 +804,19 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -1157,6 +1293,19 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -1177,6 +1326,17 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right/>
       <top style="medium">
         <color indexed="64"/>
@@ -1213,6 +1373,21 @@
         <color indexed="64"/>
       </top>
       <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1319,7 +1494,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="247">
+  <cellXfs count="275">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1342,16 +1517,13 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1360,12 +1532,19 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1378,10 +1557,11 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1390,54 +1570,55 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="18" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="19" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1466,17 +1647,22 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1486,415 +1672,434 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Нейтральный" xfId="2" builtinId="28"/>
@@ -2224,7 +2429,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -2233,10 +2438,11 @@
     <col min="4" max="4" width="16.85546875" style="2" customWidth="1"/>
     <col min="5" max="5" width="18.28515625" style="2" customWidth="1"/>
     <col min="6" max="6" width="18" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -2244,15 +2450,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -2260,93 +2466,93 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
-      <c r="F4" s="72" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A5" s="54" t="s">
+      <c r="F4" s="86" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A5" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="61"/>
-      <c r="C5" s="56" t="s">
-        <v>65</v>
-      </c>
-      <c r="D5" s="56"/>
-      <c r="E5" s="57" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5" s="59" t="s">
+      <c r="B5" s="65"/>
+      <c r="C5" s="60" t="s">
+        <v>90</v>
+      </c>
+      <c r="D5" s="60"/>
+      <c r="E5" s="61" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="63" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="55" t="s">
+    <row r="6" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="61"/>
-      <c r="C6" s="51" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="51"/>
-      <c r="E6" s="57">
+      <c r="B6" s="65"/>
+      <c r="C6" s="55" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="55"/>
+      <c r="E6" s="61">
         <v>1</v>
       </c>
-      <c r="F6" s="59" t="s">
+      <c r="F6" s="63" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="13.9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="55" t="s">
+    <row r="7" spans="1:7" ht="13.9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="59" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="65"/>
+      <c r="C7" s="54" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="54"/>
+      <c r="E7" s="62" t="s">
+        <v>89</v>
+      </c>
+      <c r="F7" s="64" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="59" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="65"/>
+      <c r="C8" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="61"/>
-      <c r="C7" s="50" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="50"/>
-      <c r="E7" s="58" t="s">
-        <v>64</v>
-      </c>
-      <c r="F7" s="60" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="55" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="61"/>
-      <c r="C8" s="51" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="51"/>
-    </row>
-    <row r="9" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="55" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" s="61"/>
-      <c r="C9" s="73" t="s">
-        <v>66</v>
-      </c>
-      <c r="D9" s="73"/>
-      <c r="E9" s="52"/>
-      <c r="F9" s="51"/>
-    </row>
-    <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="D8" s="56"/>
+      <c r="E8" s="56"/>
+      <c r="F8" s="55"/>
+    </row>
+    <row r="9" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="59" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="65"/>
+      <c r="C9" s="135" t="s">
+        <v>91</v>
+      </c>
+      <c r="D9" s="135"/>
+      <c r="E9" s="56"/>
+      <c r="F9" s="55"/>
+    </row>
+    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>0</v>
@@ -2357,366 +2563,439 @@
       <c r="D10" s="13"/>
       <c r="E10" s="14"/>
       <c r="F10" s="15"/>
-    </row>
-    <row r="11" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="17">
+      <c r="G10" s="16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="18">
         <v>3</v>
       </c>
-      <c r="C11" s="74"/>
-      <c r="D11" s="75"/>
-      <c r="E11" s="75"/>
-      <c r="F11" s="76"/>
-    </row>
-    <row r="12" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="18"/>
-      <c r="B12" s="19">
+      <c r="C11" s="136"/>
+      <c r="D11" s="137"/>
+      <c r="E11" s="137"/>
+      <c r="F11" s="138"/>
+      <c r="G11" s="67"/>
+    </row>
+    <row r="12" spans="1:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="20"/>
+      <c r="B12" s="21">
         <v>4</v>
       </c>
-      <c r="C12" s="95" t="s">
-        <v>117</v>
-      </c>
-      <c r="D12" s="96"/>
-      <c r="E12" s="96"/>
-      <c r="F12" s="97"/>
-    </row>
-    <row r="13" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="18"/>
-      <c r="B13" s="19">
+      <c r="C12" s="151" t="s">
+        <v>154</v>
+      </c>
+      <c r="D12" s="152"/>
+      <c r="E12" s="152"/>
+      <c r="F12" s="153"/>
+      <c r="G12" s="88" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="20"/>
+      <c r="B13" s="21">
         <v>5</v>
       </c>
-      <c r="C13" s="104" t="s">
-        <v>69</v>
-      </c>
-      <c r="D13" s="105"/>
-      <c r="E13" s="105"/>
-      <c r="F13" s="106"/>
-    </row>
-    <row r="14" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="20"/>
-      <c r="B14" s="21">
+      <c r="C13" s="160" t="s">
+        <v>97</v>
+      </c>
+      <c r="D13" s="161"/>
+      <c r="E13" s="161"/>
+      <c r="F13" s="162"/>
+      <c r="G13" s="88" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="22"/>
+      <c r="B14" s="23">
         <v>6</v>
       </c>
-      <c r="C14" s="86" t="s">
-        <v>118</v>
-      </c>
-      <c r="D14" s="87"/>
-      <c r="E14" s="87"/>
-      <c r="F14" s="88"/>
-    </row>
-    <row r="15" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="B15" s="17">
+      <c r="C14" s="142" t="s">
+        <v>155</v>
+      </c>
+      <c r="D14" s="143"/>
+      <c r="E14" s="143"/>
+      <c r="F14" s="144"/>
+      <c r="G14" s="90" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="18">
         <v>1</v>
       </c>
-      <c r="C15" s="89" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" s="90"/>
-      <c r="E15" s="90"/>
-      <c r="F15" s="91"/>
-    </row>
-    <row r="16" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="18"/>
-      <c r="B16" s="19">
+      <c r="C15" s="145" t="s">
+        <v>59</v>
+      </c>
+      <c r="D15" s="146"/>
+      <c r="E15" s="146"/>
+      <c r="F15" s="147"/>
+      <c r="G15" s="91" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="20"/>
+      <c r="B16" s="21">
         <v>2</v>
       </c>
-      <c r="C16" s="95" t="s">
-        <v>70</v>
-      </c>
-      <c r="D16" s="96"/>
-      <c r="E16" s="96"/>
-      <c r="F16" s="97"/>
-    </row>
-    <row r="17" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="22"/>
-      <c r="B17" s="23">
+      <c r="C16" s="151" t="s">
+        <v>98</v>
+      </c>
+      <c r="D16" s="152"/>
+      <c r="E16" s="152"/>
+      <c r="F16" s="153"/>
+      <c r="G16" s="88" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="25"/>
+      <c r="B17" s="26">
         <v>3</v>
       </c>
-      <c r="C17" s="107" t="s">
-        <v>71</v>
-      </c>
-      <c r="D17" s="108"/>
-      <c r="E17" s="108"/>
-      <c r="F17" s="109"/>
-    </row>
-    <row r="18" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="24"/>
-      <c r="B18" s="21"/>
-      <c r="C18" s="101"/>
-      <c r="D18" s="102"/>
-      <c r="E18" s="102"/>
-      <c r="F18" s="103"/>
-    </row>
-    <row r="19" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" s="17">
+      <c r="C17" s="129" t="s">
+        <v>99</v>
+      </c>
+      <c r="D17" s="130"/>
+      <c r="E17" s="130"/>
+      <c r="F17" s="131"/>
+      <c r="G17" s="88" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="27"/>
+      <c r="B18" s="23"/>
+      <c r="C18" s="157"/>
+      <c r="D18" s="158"/>
+      <c r="E18" s="158"/>
+      <c r="F18" s="159"/>
+      <c r="G18" s="24"/>
+    </row>
+    <row r="19" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="18">
         <v>2</v>
       </c>
-      <c r="C19" s="77" t="s">
+      <c r="C19" s="132" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" s="133"/>
+      <c r="E19" s="133"/>
+      <c r="F19" s="134"/>
+      <c r="G19" s="91" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="20"/>
+      <c r="B20" s="21">
+        <v>4</v>
+      </c>
+      <c r="C20" s="129" t="s">
+        <v>100</v>
+      </c>
+      <c r="D20" s="130"/>
+      <c r="E20" s="130" t="s">
+        <v>101</v>
+      </c>
+      <c r="F20" s="131"/>
+      <c r="G20" s="92" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="20"/>
+      <c r="B21" s="21">
+        <v>5</v>
+      </c>
+      <c r="C21" s="129" t="s">
+        <v>63</v>
+      </c>
+      <c r="D21" s="130"/>
+      <c r="E21" s="130"/>
+      <c r="F21" s="131"/>
+      <c r="G21" s="92" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="27"/>
+      <c r="B22" s="23">
+        <v>6</v>
+      </c>
+      <c r="C22" s="126" t="s">
+        <v>64</v>
+      </c>
+      <c r="D22" s="127"/>
+      <c r="E22" s="127"/>
+      <c r="F22" s="128"/>
+      <c r="G22" s="87" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" s="18">
+        <v>1</v>
+      </c>
+      <c r="C23" s="148"/>
+      <c r="D23" s="149"/>
+      <c r="E23" s="149"/>
+      <c r="F23" s="150"/>
+      <c r="G23" s="83"/>
+    </row>
+    <row r="24" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="20"/>
+      <c r="B24" s="21">
+        <v>2</v>
+      </c>
+      <c r="C24" s="154"/>
+      <c r="D24" s="155"/>
+      <c r="E24" s="155"/>
+      <c r="F24" s="156"/>
+      <c r="G24" s="84"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A25" s="20"/>
+      <c r="B25" s="21">
+        <v>3</v>
+      </c>
+      <c r="C25" s="101" t="s">
+        <v>96</v>
+      </c>
+      <c r="D25" s="102"/>
+      <c r="E25" s="102"/>
+      <c r="F25" s="103"/>
+      <c r="G25" s="92" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A26" s="25"/>
+      <c r="B26" s="26">
+        <v>4</v>
+      </c>
+      <c r="C26" s="129" t="s">
+        <v>102</v>
+      </c>
+      <c r="D26" s="130"/>
+      <c r="E26" s="130"/>
+      <c r="F26" s="131"/>
+      <c r="G26" s="88" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A27" s="27"/>
+      <c r="B27" s="23">
+        <v>5</v>
+      </c>
+      <c r="C27" s="107" t="s">
+        <v>103</v>
+      </c>
+      <c r="D27" s="108"/>
+      <c r="E27" s="108"/>
+      <c r="F27" s="109"/>
+      <c r="G27" s="90" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" s="18">
+        <v>3</v>
+      </c>
+      <c r="C28" s="139" t="s">
+        <v>31</v>
+      </c>
+      <c r="D28" s="140"/>
+      <c r="E28" s="140"/>
+      <c r="F28" s="141"/>
+      <c r="G28" s="88" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="28"/>
+      <c r="B29" s="21">
+        <v>5</v>
+      </c>
+      <c r="C29" s="101" t="s">
+        <v>150</v>
+      </c>
+      <c r="D29" s="102"/>
+      <c r="E29" s="102"/>
+      <c r="F29" s="103"/>
+      <c r="G29" s="97" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="28"/>
+      <c r="B30" s="21">
+        <v>6</v>
+      </c>
+      <c r="C30" s="101" t="s">
+        <v>151</v>
+      </c>
+      <c r="D30" s="102"/>
+      <c r="E30" s="102"/>
+      <c r="F30" s="103"/>
+      <c r="G30" s="97" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="29"/>
+      <c r="B31" s="26"/>
+      <c r="C31" s="110"/>
+      <c r="D31" s="111"/>
+      <c r="E31" s="111"/>
+      <c r="F31" s="112"/>
+      <c r="G31" s="72"/>
+    </row>
+    <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="78"/>
-      <c r="E19" s="78"/>
-      <c r="F19" s="79"/>
-    </row>
-    <row r="20" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="18"/>
-      <c r="B20" s="19">
+      <c r="B32" s="18">
+        <v>1</v>
+      </c>
+      <c r="C32" s="132" t="s">
+        <v>34</v>
+      </c>
+      <c r="D32" s="133"/>
+      <c r="E32" s="133"/>
+      <c r="F32" s="134"/>
+      <c r="G32" s="19"/>
+    </row>
+    <row r="33" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="31"/>
+      <c r="B33" s="21">
+        <v>2</v>
+      </c>
+      <c r="C33" s="113"/>
+      <c r="D33" s="114"/>
+      <c r="E33" s="114"/>
+      <c r="F33" s="115"/>
+      <c r="G33" s="88"/>
+    </row>
+    <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="31"/>
+      <c r="B34" s="21">
+        <v>3</v>
+      </c>
+      <c r="C34" s="113"/>
+      <c r="D34" s="114"/>
+      <c r="E34" s="114"/>
+      <c r="F34" s="115"/>
+      <c r="G34" s="88"/>
+    </row>
+    <row r="35" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="32"/>
+      <c r="B35" s="23">
         <v>4</v>
       </c>
-      <c r="C20" s="107" t="s">
-        <v>72</v>
-      </c>
-      <c r="D20" s="108"/>
-      <c r="E20" s="108" t="s">
-        <v>73</v>
-      </c>
-      <c r="F20" s="109"/>
-    </row>
-    <row r="21" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="18"/>
-      <c r="B21" s="19">
-        <v>5</v>
-      </c>
-      <c r="C21" s="107" t="s">
-        <v>46</v>
-      </c>
-      <c r="D21" s="108"/>
-      <c r="E21" s="108"/>
-      <c r="F21" s="109"/>
-    </row>
-    <row r="22" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="24"/>
-      <c r="B22" s="21">
-        <v>6</v>
-      </c>
-      <c r="C22" s="110" t="s">
-        <v>47</v>
-      </c>
-      <c r="D22" s="111"/>
-      <c r="E22" s="111"/>
-      <c r="F22" s="112"/>
-    </row>
-    <row r="23" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="B23" s="17">
-        <v>1</v>
-      </c>
-      <c r="C23" s="92"/>
-      <c r="D23" s="93"/>
-      <c r="E23" s="93"/>
-      <c r="F23" s="94"/>
-    </row>
-    <row r="24" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="18"/>
-      <c r="B24" s="19">
-        <v>2</v>
-      </c>
-      <c r="C24" s="98"/>
-      <c r="D24" s="99"/>
-      <c r="E24" s="99"/>
-      <c r="F24" s="100"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A25" s="18"/>
-      <c r="B25" s="19">
-        <v>3</v>
-      </c>
-      <c r="C25" s="80" t="s">
-        <v>68</v>
-      </c>
-      <c r="D25" s="81"/>
-      <c r="E25" s="81"/>
-      <c r="F25" s="82"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A26" s="22"/>
-      <c r="B26" s="23">
-        <v>4</v>
-      </c>
-      <c r="C26" s="107" t="s">
-        <v>74</v>
-      </c>
-      <c r="D26" s="108"/>
-      <c r="E26" s="108"/>
-      <c r="F26" s="109"/>
-    </row>
-    <row r="27" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="24"/>
-      <c r="B27" s="21">
-        <v>5</v>
-      </c>
-      <c r="C27" s="126" t="s">
-        <v>75</v>
-      </c>
-      <c r="D27" s="127"/>
-      <c r="E27" s="127"/>
-      <c r="F27" s="128"/>
-    </row>
-    <row r="28" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="B28" s="17">
-        <v>3</v>
-      </c>
-      <c r="C28" s="83" t="s">
-        <v>30</v>
-      </c>
-      <c r="D28" s="84"/>
-      <c r="E28" s="84"/>
-      <c r="F28" s="85"/>
-    </row>
-    <row r="29" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="25"/>
-      <c r="B29" s="19">
-        <v>5</v>
-      </c>
-      <c r="C29" s="80" t="s">
-        <v>113</v>
-      </c>
-      <c r="D29" s="81"/>
-      <c r="E29" s="81"/>
-      <c r="F29" s="82"/>
-    </row>
-    <row r="30" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="25"/>
-      <c r="B30" s="19">
-        <v>6</v>
-      </c>
-      <c r="C30" s="80" t="s">
-        <v>114</v>
-      </c>
-      <c r="D30" s="81"/>
-      <c r="E30" s="81"/>
-      <c r="F30" s="82"/>
-    </row>
-    <row r="31" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="26"/>
-      <c r="B31" s="23"/>
-      <c r="C31" s="129"/>
-      <c r="D31" s="130"/>
-      <c r="E31" s="130"/>
-      <c r="F31" s="131"/>
-    </row>
-    <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="B32" s="17">
-        <v>1</v>
-      </c>
-      <c r="C32" s="77" t="s">
+      <c r="C35" s="123"/>
+      <c r="D35" s="124"/>
+      <c r="E35" s="124"/>
+      <c r="F35" s="125"/>
+      <c r="G35" s="92"/>
+    </row>
+    <row r="36" spans="1:7" s="35" customFormat="1" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="33"/>
+      <c r="B36" s="34"/>
+      <c r="C36" s="122"/>
+      <c r="D36" s="122"/>
+      <c r="E36" s="122"/>
+      <c r="F36" s="122"/>
+      <c r="G36" s="81"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A37" s="36"/>
+      <c r="B37" s="74" t="s">
         <v>33</v>
       </c>
-      <c r="D32" s="78"/>
-      <c r="E32" s="78"/>
-      <c r="F32" s="79"/>
-    </row>
-    <row r="33" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="28"/>
-      <c r="B33" s="19">
-        <v>2</v>
-      </c>
-      <c r="C33" s="132"/>
-      <c r="D33" s="133"/>
-      <c r="E33" s="133"/>
-      <c r="F33" s="134"/>
-    </row>
-    <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="28"/>
-      <c r="B34" s="19">
-        <v>3</v>
-      </c>
-      <c r="C34" s="132"/>
-      <c r="D34" s="133"/>
-      <c r="E34" s="133"/>
-      <c r="F34" s="134"/>
-    </row>
-    <row r="35" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="29"/>
-      <c r="B35" s="21">
-        <v>4</v>
-      </c>
-      <c r="C35" s="120"/>
-      <c r="D35" s="121"/>
-      <c r="E35" s="121"/>
-      <c r="F35" s="122"/>
-    </row>
-    <row r="36" spans="1:6" s="32" customFormat="1" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="30"/>
-      <c r="B36" s="31"/>
-      <c r="C36" s="119"/>
-      <c r="D36" s="119"/>
-      <c r="E36" s="119"/>
-      <c r="F36" s="119"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A37" s="33"/>
-      <c r="B37" s="66" t="s">
-        <v>32</v>
-      </c>
-      <c r="C37" s="123" t="s">
-        <v>45</v>
-      </c>
-      <c r="D37" s="124"/>
-      <c r="E37" s="124"/>
-      <c r="F37" s="125"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A38" s="62"/>
-      <c r="B38" s="35" t="s">
-        <v>32</v>
-      </c>
-      <c r="C38" s="116" t="s">
-        <v>43</v>
-      </c>
-      <c r="D38" s="117"/>
-      <c r="E38" s="117"/>
-      <c r="F38" s="118"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A39" s="34"/>
-      <c r="B39" s="35" t="s">
-        <v>32</v>
-      </c>
-      <c r="C39" s="116" t="s">
-        <v>36</v>
-      </c>
-      <c r="D39" s="117"/>
-      <c r="E39" s="117"/>
-      <c r="F39" s="118"/>
-    </row>
-    <row r="40" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A40" s="36"/>
-      <c r="B40" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="C40" s="113" t="s">
+      <c r="C37" s="104" t="s">
+        <v>60</v>
+      </c>
+      <c r="D37" s="105"/>
+      <c r="E37" s="105"/>
+      <c r="F37" s="106"/>
+      <c r="G37" s="91" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A38" s="66"/>
+      <c r="B38" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" s="119" t="s">
+        <v>58</v>
+      </c>
+      <c r="D38" s="120"/>
+      <c r="E38" s="120"/>
+      <c r="F38" s="121"/>
+      <c r="G38" s="89" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A39" s="37"/>
+      <c r="B39" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="C39" s="119" t="s">
+        <v>38</v>
+      </c>
+      <c r="D39" s="120"/>
+      <c r="E39" s="120"/>
+      <c r="F39" s="121"/>
+      <c r="G39" s="88" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A40" s="40"/>
+      <c r="B40" s="41" t="s">
+        <v>33</v>
+      </c>
+      <c r="C40" s="116" t="s">
+        <v>42</v>
+      </c>
+      <c r="D40" s="117"/>
+      <c r="E40" s="117"/>
+      <c r="F40" s="118"/>
+      <c r="G40" s="75" t="s">
         <v>37</v>
       </c>
-      <c r="D40" s="114"/>
-      <c r="E40" s="114"/>
-      <c r="F40" s="115"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.4">
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A42" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.4">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A43" s="2" t="s">
         <v>15</v>
       </c>
@@ -2726,22 +3005,6 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C40:F40"/>
-    <mergeCell ref="C39:F39"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C11:F11"/>
     <mergeCell ref="C32:F32"/>
@@ -2758,6 +3021,22 @@
     <mergeCell ref="C13:F13"/>
     <mergeCell ref="C26:F26"/>
     <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="C40:F40"/>
+    <mergeCell ref="C39:F39"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C33:F33"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C6"/>
@@ -2795,7 +3074,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -2804,10 +3083,11 @@
     <col min="4" max="4" width="17.85546875" style="2" customWidth="1"/>
     <col min="5" max="5" width="19.5703125" style="2" customWidth="1"/>
     <col min="6" max="6" width="18.85546875" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -2815,15 +3095,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -2831,444 +3111,513 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
-      <c r="F4" s="72" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A5" s="54" t="s">
+      <c r="F4" s="86" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A5" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="61"/>
-      <c r="C5" s="56" t="s">
-        <v>65</v>
-      </c>
-      <c r="D5" s="56"/>
-      <c r="E5" s="57" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5" s="59" t="s">
+      <c r="B5" s="65"/>
+      <c r="C5" s="60" t="s">
+        <v>90</v>
+      </c>
+      <c r="D5" s="60"/>
+      <c r="E5" s="61" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="63" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A6" s="55" t="s">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A6" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="61"/>
-      <c r="C6" s="51" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="51"/>
-      <c r="E6" s="57">
+      <c r="B6" s="65"/>
+      <c r="C6" s="55" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="55"/>
+      <c r="E6" s="61">
         <v>2</v>
       </c>
-      <c r="F6" s="59" t="s">
+      <c r="F6" s="63" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A7" s="55" t="s">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A7" s="59" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="65"/>
+      <c r="C7" s="54" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="54"/>
+      <c r="E7" s="62" t="s">
+        <v>57</v>
+      </c>
+      <c r="F7" s="64" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A8" s="59" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="65"/>
+      <c r="C8" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="61"/>
-      <c r="C7" s="50" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="50"/>
-      <c r="E7" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="F7" s="60" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A8" s="55" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="61"/>
-      <c r="C8" s="51" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="51"/>
-    </row>
-    <row r="9" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="D8" s="56"/>
+      <c r="E8" s="56"/>
+      <c r="F8" s="55"/>
+    </row>
+    <row r="9" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="73" t="s">
-        <v>66</v>
-      </c>
-      <c r="D9" s="73"/>
+        <v>36</v>
+      </c>
+      <c r="C9" s="135" t="s">
+        <v>91</v>
+      </c>
+      <c r="D9" s="135"/>
       <c r="E9" s="9"/>
       <c r="F9" s="8"/>
     </row>
-    <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" s="39" t="s">
+    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="40" t="s">
+      <c r="C10" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="D10" s="41"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="43"/>
-    </row>
-    <row r="11" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="44" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="45">
+      <c r="D10" s="45"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="47"/>
+      <c r="G10" s="16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="48" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="49">
         <v>3</v>
       </c>
-      <c r="C11" s="149" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" s="150"/>
-      <c r="E11" s="150"/>
-      <c r="F11" s="151"/>
-    </row>
-    <row r="12" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="18"/>
-      <c r="B12" s="19">
+      <c r="C11" s="178" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="179"/>
+      <c r="E11" s="179"/>
+      <c r="F11" s="180"/>
+      <c r="G11" s="91"/>
+    </row>
+    <row r="12" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="20"/>
+      <c r="B12" s="21">
         <v>5</v>
       </c>
-      <c r="C12" s="95" t="s">
-        <v>77</v>
-      </c>
-      <c r="D12" s="96"/>
-      <c r="E12" s="96"/>
-      <c r="F12" s="97"/>
-    </row>
-    <row r="13" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="18"/>
-      <c r="B13" s="19">
+      <c r="C12" s="151" t="s">
+        <v>107</v>
+      </c>
+      <c r="D12" s="152"/>
+      <c r="E12" s="152"/>
+      <c r="F12" s="153"/>
+      <c r="G12" s="88" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="20"/>
+      <c r="B13" s="21">
         <v>6</v>
       </c>
-      <c r="C13" s="95" t="s">
-        <v>78</v>
-      </c>
-      <c r="D13" s="96"/>
-      <c r="E13" s="96"/>
-      <c r="F13" s="97"/>
-    </row>
-    <row r="14" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="20"/>
-      <c r="B14" s="21">
+      <c r="C13" s="151" t="s">
+        <v>108</v>
+      </c>
+      <c r="D13" s="152"/>
+      <c r="E13" s="152"/>
+      <c r="F13" s="153"/>
+      <c r="G13" s="88" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="22"/>
+      <c r="B14" s="23">
         <v>7</v>
       </c>
-      <c r="C14" s="135" t="s">
-        <v>119</v>
-      </c>
-      <c r="D14" s="136"/>
-      <c r="E14" s="136"/>
-      <c r="F14" s="137"/>
-    </row>
-    <row r="15" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="B15" s="17">
+      <c r="C14" s="192" t="s">
+        <v>157</v>
+      </c>
+      <c r="D14" s="193"/>
+      <c r="E14" s="193"/>
+      <c r="F14" s="194"/>
+      <c r="G14" s="98" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="18">
         <v>1</v>
       </c>
-      <c r="C15" s="141" t="s">
-        <v>79</v>
-      </c>
-      <c r="D15" s="142"/>
-      <c r="E15" s="142"/>
-      <c r="F15" s="143"/>
-    </row>
-    <row r="16" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="18"/>
-      <c r="B16" s="19">
+      <c r="C15" s="181" t="s">
+        <v>110</v>
+      </c>
+      <c r="D15" s="182"/>
+      <c r="E15" s="182"/>
+      <c r="F15" s="183"/>
+      <c r="G15" s="91" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="20"/>
+      <c r="B16" s="21">
         <v>2</v>
       </c>
-      <c r="C16" s="80" t="s">
-        <v>48</v>
-      </c>
-      <c r="D16" s="81"/>
-      <c r="E16" s="81"/>
-      <c r="F16" s="82"/>
-    </row>
-    <row r="17" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="18"/>
-      <c r="B17" s="19">
+      <c r="C16" s="101" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16" s="102"/>
+      <c r="E16" s="102"/>
+      <c r="F16" s="103"/>
+      <c r="G16" s="94" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="20"/>
+      <c r="B17" s="21">
         <v>3</v>
       </c>
-      <c r="C17" s="152" t="s">
-        <v>80</v>
-      </c>
-      <c r="D17" s="153"/>
-      <c r="E17" s="153"/>
-      <c r="F17" s="154"/>
-    </row>
-    <row r="18" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="24"/>
-      <c r="B18" s="21">
+      <c r="C17" s="169" t="s">
+        <v>111</v>
+      </c>
+      <c r="D17" s="170"/>
+      <c r="E17" s="170"/>
+      <c r="F17" s="171"/>
+      <c r="G17" s="94" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="27"/>
+      <c r="B18" s="23">
         <v>4</v>
       </c>
-      <c r="C18" s="113" t="s">
-        <v>41</v>
-      </c>
-      <c r="D18" s="114"/>
-      <c r="E18" s="114"/>
-      <c r="F18" s="115"/>
-    </row>
-    <row r="19" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" s="17">
+      <c r="C18" s="116" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="117"/>
+      <c r="E18" s="117"/>
+      <c r="F18" s="118"/>
+      <c r="G18" s="87" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="18">
         <v>3</v>
       </c>
-      <c r="C19" s="146"/>
-      <c r="D19" s="147"/>
-      <c r="E19" s="147"/>
-      <c r="F19" s="148"/>
-    </row>
-    <row r="20" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="18"/>
-      <c r="B20" s="45">
+      <c r="C19" s="186"/>
+      <c r="D19" s="187"/>
+      <c r="E19" s="187"/>
+      <c r="F19" s="188"/>
+      <c r="G19" s="91"/>
+    </row>
+    <row r="20" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="20"/>
+      <c r="B20" s="49">
         <v>4</v>
       </c>
-      <c r="C20" s="132"/>
-      <c r="D20" s="144"/>
-      <c r="E20" s="145" t="s">
-        <v>50</v>
-      </c>
-      <c r="F20" s="82"/>
-    </row>
-    <row r="21" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="18"/>
-      <c r="B21" s="19">
+      <c r="C20" s="113"/>
+      <c r="D20" s="184"/>
+      <c r="E20" s="185" t="s">
+        <v>70</v>
+      </c>
+      <c r="F20" s="103"/>
+      <c r="G20" s="89" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="20"/>
+      <c r="B21" s="21">
         <v>5</v>
       </c>
-      <c r="C21" s="107" t="s">
+      <c r="C21" s="129" t="s">
+        <v>71</v>
+      </c>
+      <c r="D21" s="130"/>
+      <c r="E21" s="130" t="s">
+        <v>101</v>
+      </c>
+      <c r="F21" s="131"/>
+      <c r="G21" s="88" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="27"/>
+      <c r="B22" s="23">
+        <v>6</v>
+      </c>
+      <c r="C22" s="116" t="s">
+        <v>113</v>
+      </c>
+      <c r="D22" s="195"/>
+      <c r="E22" s="196"/>
+      <c r="F22" s="165"/>
+      <c r="G22" s="87" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" s="49">
+        <v>1</v>
+      </c>
+      <c r="C23" s="189"/>
+      <c r="D23" s="190"/>
+      <c r="E23" s="190"/>
+      <c r="F23" s="191"/>
+      <c r="G23" s="19"/>
+    </row>
+    <row r="24" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="20"/>
+      <c r="B24" s="21">
+        <v>2</v>
+      </c>
+      <c r="C24" s="151" t="s">
+        <v>69</v>
+      </c>
+      <c r="D24" s="152"/>
+      <c r="E24" s="152"/>
+      <c r="F24" s="153"/>
+      <c r="G24" s="88" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="20"/>
+      <c r="B25" s="21">
+        <v>3</v>
+      </c>
+      <c r="C25" s="169" t="s">
+        <v>31</v>
+      </c>
+      <c r="D25" s="170"/>
+      <c r="E25" s="170"/>
+      <c r="F25" s="171"/>
+      <c r="G25" s="94"/>
+    </row>
+    <row r="26" spans="1:7" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="27"/>
+      <c r="B26" s="23"/>
+      <c r="C26" s="166"/>
+      <c r="D26" s="167"/>
+      <c r="E26" s="167"/>
+      <c r="F26" s="168"/>
+      <c r="G26" s="90"/>
+    </row>
+    <row r="27" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" s="18">
+        <v>3</v>
+      </c>
+      <c r="C27" s="178" t="s">
+        <v>114</v>
+      </c>
+      <c r="D27" s="179"/>
+      <c r="E27" s="179"/>
+      <c r="F27" s="180"/>
+      <c r="G27" s="91" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="28"/>
+      <c r="B28" s="21">
+        <v>4</v>
+      </c>
+      <c r="C28" s="169" t="s">
+        <v>123</v>
+      </c>
+      <c r="D28" s="170"/>
+      <c r="E28" s="170"/>
+      <c r="F28" s="171"/>
+      <c r="G28" s="94" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="28"/>
+      <c r="B29" s="21">
+        <v>5</v>
+      </c>
+      <c r="C29" s="169" t="s">
+        <v>124</v>
+      </c>
+      <c r="D29" s="170"/>
+      <c r="E29" s="170"/>
+      <c r="F29" s="171"/>
+      <c r="G29" s="94" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="50"/>
+      <c r="B30" s="23">
+        <v>6</v>
+      </c>
+      <c r="C30" s="172" t="s">
+        <v>125</v>
+      </c>
+      <c r="D30" s="173"/>
+      <c r="E30" s="173"/>
+      <c r="F30" s="174"/>
+      <c r="G30" s="90" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A31" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="18">
+        <v>1</v>
+      </c>
+      <c r="C31" s="104"/>
+      <c r="D31" s="105"/>
+      <c r="E31" s="105"/>
+      <c r="F31" s="106"/>
+      <c r="G31" s="93"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A32" s="31"/>
+      <c r="B32" s="21">
+        <v>2</v>
+      </c>
+      <c r="C32" s="129" t="s">
+        <v>84</v>
+      </c>
+      <c r="D32" s="130"/>
+      <c r="E32" s="130"/>
+      <c r="F32" s="131"/>
+      <c r="G32" s="88" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A33" s="31"/>
+      <c r="B33" s="21">
+        <v>3</v>
+      </c>
+      <c r="C33" s="154"/>
+      <c r="D33" s="155"/>
+      <c r="E33" s="155"/>
+      <c r="F33" s="156"/>
+      <c r="G33" s="88"/>
+    </row>
+    <row r="34" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="32"/>
+      <c r="B34" s="23">
+        <v>4</v>
+      </c>
+      <c r="C34" s="163"/>
+      <c r="D34" s="164"/>
+      <c r="E34" s="164"/>
+      <c r="F34" s="165"/>
+      <c r="G34" s="24"/>
+    </row>
+    <row r="35" spans="1:7" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="68"/>
+      <c r="B35" s="69"/>
+      <c r="C35" s="175"/>
+      <c r="D35" s="176"/>
+      <c r="E35" s="176"/>
+      <c r="F35" s="177"/>
+      <c r="G35" s="70"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A36" s="36"/>
+      <c r="B36" s="74" t="s">
+        <v>33</v>
+      </c>
+      <c r="C36" s="104" t="s">
         <v>51</v>
       </c>
-      <c r="D21" s="108"/>
-      <c r="E21" s="108" t="s">
-        <v>73</v>
-      </c>
-      <c r="F21" s="109"/>
-    </row>
-    <row r="22" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="24"/>
-      <c r="B22" s="21">
-        <v>6</v>
-      </c>
-      <c r="C22" s="113" t="s">
-        <v>81</v>
-      </c>
-      <c r="D22" s="138"/>
-      <c r="E22" s="139"/>
-      <c r="F22" s="140"/>
-    </row>
-    <row r="23" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="B23" s="45">
-        <v>1</v>
-      </c>
-      <c r="C23" s="155"/>
-      <c r="D23" s="156"/>
-      <c r="E23" s="156"/>
-      <c r="F23" s="157"/>
-    </row>
-    <row r="24" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="18"/>
-      <c r="B24" s="19">
-        <v>2</v>
-      </c>
-      <c r="C24" s="95" t="s">
+      <c r="D36" s="105"/>
+      <c r="E36" s="105"/>
+      <c r="F36" s="106"/>
+      <c r="G36" s="93" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A37" s="37"/>
+      <c r="B37" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="C37" s="101" t="s">
+        <v>52</v>
+      </c>
+      <c r="D37" s="120"/>
+      <c r="E37" s="120"/>
+      <c r="F37" s="121"/>
+      <c r="G37" s="94" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="40"/>
+      <c r="B38" s="41" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" s="116" t="s">
+        <v>106</v>
+      </c>
+      <c r="D38" s="117"/>
+      <c r="E38" s="117"/>
+      <c r="F38" s="118"/>
+      <c r="G38" s="90" t="s">
         <v>49</v>
       </c>
-      <c r="D24" s="96"/>
-      <c r="E24" s="96"/>
-      <c r="F24" s="97"/>
-    </row>
-    <row r="25" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="18"/>
-      <c r="B25" s="19">
-        <v>3</v>
-      </c>
-      <c r="C25" s="152" t="s">
-        <v>30</v>
-      </c>
-      <c r="D25" s="153"/>
-      <c r="E25" s="153"/>
-      <c r="F25" s="154"/>
-    </row>
-    <row r="26" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="24"/>
-      <c r="B26" s="21"/>
-      <c r="C26" s="160"/>
-      <c r="D26" s="161"/>
-      <c r="E26" s="161"/>
-      <c r="F26" s="162"/>
-    </row>
-    <row r="27" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="B27" s="17">
-        <v>3</v>
-      </c>
-      <c r="C27" s="149" t="s">
-        <v>82</v>
-      </c>
-      <c r="D27" s="150"/>
-      <c r="E27" s="150"/>
-      <c r="F27" s="151"/>
-    </row>
-    <row r="28" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="25"/>
-      <c r="B28" s="19">
-        <v>4</v>
-      </c>
-      <c r="C28" s="152" t="s">
-        <v>89</v>
-      </c>
-      <c r="D28" s="153"/>
-      <c r="E28" s="153"/>
-      <c r="F28" s="154"/>
-    </row>
-    <row r="29" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="25"/>
-      <c r="B29" s="19">
-        <v>5</v>
-      </c>
-      <c r="C29" s="152" t="s">
-        <v>90</v>
-      </c>
-      <c r="D29" s="153"/>
-      <c r="E29" s="153"/>
-      <c r="F29" s="154"/>
-    </row>
-    <row r="30" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="46"/>
-      <c r="B30" s="21">
-        <v>6</v>
-      </c>
-      <c r="C30" s="163" t="s">
-        <v>91</v>
-      </c>
-      <c r="D30" s="164"/>
-      <c r="E30" s="164"/>
-      <c r="F30" s="165"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A31" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="B31" s="17">
-        <v>1</v>
-      </c>
-      <c r="C31" s="123"/>
-      <c r="D31" s="124"/>
-      <c r="E31" s="124"/>
-      <c r="F31" s="125"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A32" s="28"/>
-      <c r="B32" s="19">
-        <v>2</v>
-      </c>
-      <c r="C32" s="107" t="s">
-        <v>59</v>
-      </c>
-      <c r="D32" s="108"/>
-      <c r="E32" s="108"/>
-      <c r="F32" s="109"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A33" s="28"/>
-      <c r="B33" s="19">
-        <v>3</v>
-      </c>
-      <c r="C33" s="98"/>
-      <c r="D33" s="99"/>
-      <c r="E33" s="99"/>
-      <c r="F33" s="100"/>
-    </row>
-    <row r="34" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="29"/>
-      <c r="B34" s="21">
-        <v>4</v>
-      </c>
-      <c r="C34" s="158"/>
-      <c r="D34" s="159"/>
-      <c r="E34" s="159"/>
-      <c r="F34" s="140"/>
-    </row>
-    <row r="35" spans="1:6" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="63"/>
-      <c r="B35" s="64"/>
-      <c r="C35" s="166"/>
-      <c r="D35" s="167"/>
-      <c r="E35" s="167"/>
-      <c r="F35" s="168"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A36" s="33"/>
-      <c r="B36" s="66" t="s">
-        <v>32</v>
-      </c>
-      <c r="C36" s="123" t="s">
-        <v>39</v>
-      </c>
-      <c r="D36" s="124"/>
-      <c r="E36" s="124"/>
-      <c r="F36" s="125"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A37" s="34"/>
-      <c r="B37" s="35" t="s">
-        <v>32</v>
-      </c>
-      <c r="C37" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="D37" s="117"/>
-      <c r="E37" s="117"/>
-      <c r="F37" s="118"/>
-    </row>
-    <row r="38" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="36"/>
-      <c r="B38" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="C38" s="113" t="s">
-        <v>76</v>
-      </c>
-      <c r="D38" s="114"/>
-      <c r="E38" s="114"/>
-      <c r="F38" s="115"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A40" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.4">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A41" s="2" t="s">
         <v>15</v>
       </c>
@@ -3278,17 +3627,11 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C32:F32"/>
     <mergeCell ref="C33:F33"/>
@@ -3305,11 +3648,17 @@
     <mergeCell ref="E21:F21"/>
     <mergeCell ref="C23:F23"/>
     <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="C27:F27"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5">
@@ -3361,7 +3710,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:L38"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -3370,10 +3719,11 @@
     <col min="4" max="4" width="17.140625" style="2" customWidth="1"/>
     <col min="5" max="5" width="17.7109375" style="2" customWidth="1"/>
     <col min="6" max="6" width="17.5703125" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -3381,15 +3731,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -3397,90 +3747,90 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
-      <c r="F4" s="72" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A5" s="54" t="s">
+      <c r="F4" s="86" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A5" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="56" t="s">
-        <v>65</v>
-      </c>
-      <c r="D5" s="56"/>
-      <c r="E5" s="57" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5" s="59" t="s">
+      <c r="C5" s="60" t="s">
+        <v>90</v>
+      </c>
+      <c r="D5" s="60"/>
+      <c r="E5" s="61" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="63" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A6" s="55" t="s">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A6" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="51" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="51"/>
-      <c r="E6" s="57">
+      <c r="C6" s="55" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="55"/>
+      <c r="E6" s="61">
         <v>3</v>
       </c>
-      <c r="F6" s="59" t="s">
+      <c r="F6" s="63" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A7" s="55" t="s">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A7" s="59" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="54" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="54"/>
+      <c r="E7" s="62" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" s="64" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="59" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="50" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="50"/>
-      <c r="E7" s="58" t="s">
-        <v>38</v>
-      </c>
-      <c r="F7" s="60" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="55" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="51" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="52"/>
+      <c r="D8" s="56"/>
       <c r="E8" s="9"/>
       <c r="F8" s="8"/>
     </row>
-    <row r="9" spans="1:11" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:12" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="73" t="s">
-        <v>66</v>
-      </c>
-      <c r="D9" s="73"/>
+        <v>36</v>
+      </c>
+      <c r="C9" s="135" t="s">
+        <v>91</v>
+      </c>
+      <c r="D9" s="135"/>
       <c r="E9" s="9"/>
       <c r="F9" s="8"/>
     </row>
-    <row r="10" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" s="39" t="s">
+    <row r="10" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="43" t="s">
         <v>0</v>
       </c>
       <c r="C10" s="12" t="s">
@@ -3489,323 +3839,384 @@
       <c r="D10" s="13"/>
       <c r="E10" s="14"/>
       <c r="F10" s="15"/>
-    </row>
-    <row r="11" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="44" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="45">
+      <c r="G10" s="16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="48" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="49">
         <v>1</v>
       </c>
-      <c r="C11" s="155"/>
-      <c r="D11" s="156"/>
-      <c r="E11" s="156"/>
-      <c r="F11" s="157"/>
-    </row>
-    <row r="12" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="18"/>
-      <c r="B12" s="19">
+      <c r="C11" s="189"/>
+      <c r="D11" s="190"/>
+      <c r="E11" s="190"/>
+      <c r="F11" s="191"/>
+      <c r="G11" s="91"/>
+    </row>
+    <row r="12" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="20"/>
+      <c r="B12" s="21">
         <v>2</v>
       </c>
-      <c r="C12" s="184"/>
-      <c r="D12" s="185"/>
-      <c r="E12" s="185"/>
-      <c r="F12" s="186"/>
-    </row>
-    <row r="13" spans="1:11" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="18"/>
-      <c r="B13" s="19">
+      <c r="C12" s="198"/>
+      <c r="D12" s="199"/>
+      <c r="E12" s="199"/>
+      <c r="F12" s="200"/>
+      <c r="G12" s="88"/>
+    </row>
+    <row r="13" spans="1:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="20"/>
+      <c r="B13" s="21">
         <v>3</v>
       </c>
-      <c r="C13" s="184" t="s">
+      <c r="C13" s="198" t="s">
+        <v>117</v>
+      </c>
+      <c r="D13" s="199"/>
+      <c r="E13" s="199"/>
+      <c r="F13" s="200"/>
+      <c r="G13" s="88" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="22"/>
+      <c r="B14" s="71">
+        <v>4</v>
+      </c>
+      <c r="C14" s="207"/>
+      <c r="D14" s="208"/>
+      <c r="E14" s="208"/>
+      <c r="F14" s="209"/>
+      <c r="G14" s="82"/>
+    </row>
+    <row r="15" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="76" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" s="204" t="s">
+        <v>73</v>
+      </c>
+      <c r="D15" s="205"/>
+      <c r="E15" s="205"/>
+      <c r="F15" s="206"/>
+      <c r="G15" s="19"/>
+      <c r="L15" s="57"/>
+    </row>
+    <row r="16" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="20"/>
+      <c r="B16" s="21">
+        <v>4</v>
+      </c>
+      <c r="C16" s="151" t="s">
+        <v>119</v>
+      </c>
+      <c r="D16" s="152"/>
+      <c r="E16" s="152"/>
+      <c r="F16" s="153"/>
+      <c r="G16" s="94" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="20"/>
+      <c r="B17" s="21">
+        <v>5</v>
+      </c>
+      <c r="C17" s="151" t="s">
+        <v>120</v>
+      </c>
+      <c r="D17" s="152"/>
+      <c r="E17" s="152"/>
+      <c r="F17" s="153"/>
+      <c r="G17" s="94" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="27"/>
+      <c r="B18" s="23">
+        <v>6</v>
+      </c>
+      <c r="C18" s="107" t="s">
+        <v>161</v>
+      </c>
+      <c r="D18" s="108"/>
+      <c r="E18" s="108"/>
+      <c r="F18" s="109"/>
+      <c r="G18" s="100" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A19" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="18">
+        <v>1</v>
+      </c>
+      <c r="C19" s="227"/>
+      <c r="D19" s="228"/>
+      <c r="E19" s="228"/>
+      <c r="F19" s="229"/>
+      <c r="G19" s="93"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A20" s="20"/>
+      <c r="B20" s="21">
+        <v>2</v>
+      </c>
+      <c r="C20" s="169" t="s">
+        <v>128</v>
+      </c>
+      <c r="D20" s="170"/>
+      <c r="E20" s="170"/>
+      <c r="F20" s="171"/>
+      <c r="G20" s="94" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="20"/>
+      <c r="B21" s="21">
+        <v>3</v>
+      </c>
+      <c r="C21" s="169" t="s">
+        <v>129</v>
+      </c>
+      <c r="D21" s="170"/>
+      <c r="E21" s="170"/>
+      <c r="F21" s="171"/>
+      <c r="G21" s="94" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="27"/>
+      <c r="B22" s="23">
+        <v>4</v>
+      </c>
+      <c r="C22" s="210"/>
+      <c r="D22" s="211"/>
+      <c r="E22" s="211"/>
+      <c r="F22" s="212"/>
+      <c r="G22" s="90"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A23" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" s="18">
+        <v>2</v>
+      </c>
+      <c r="C23" s="213"/>
+      <c r="D23" s="214"/>
+      <c r="E23" s="214"/>
+      <c r="F23" s="215"/>
+      <c r="G23" s="85"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A24" s="20"/>
+      <c r="B24" s="21">
+        <v>3</v>
+      </c>
+      <c r="C24" s="201" t="s">
+        <v>130</v>
+      </c>
+      <c r="D24" s="202"/>
+      <c r="E24" s="202"/>
+      <c r="F24" s="203"/>
+      <c r="G24" s="88" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A25" s="20"/>
+      <c r="B25" s="21">
+        <v>4</v>
+      </c>
+      <c r="C25" s="201" t="s">
+        <v>131</v>
+      </c>
+      <c r="D25" s="202"/>
+      <c r="E25" s="202"/>
+      <c r="F25" s="203"/>
+      <c r="G25" s="88" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="27"/>
+      <c r="B26" s="23">
+        <v>5</v>
+      </c>
+      <c r="C26" s="207"/>
+      <c r="D26" s="208"/>
+      <c r="E26" s="216" t="s">
+        <v>118</v>
+      </c>
+      <c r="F26" s="217"/>
+      <c r="G26" s="88" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" s="18">
+        <v>2</v>
+      </c>
+      <c r="C27" s="227" t="s">
+        <v>121</v>
+      </c>
+      <c r="D27" s="228"/>
+      <c r="E27" s="228"/>
+      <c r="F27" s="229"/>
+      <c r="G27" s="93" t="s">
         <v>83</v>
       </c>
-      <c r="D13" s="185"/>
-      <c r="E13" s="185"/>
-      <c r="F13" s="186"/>
-    </row>
-    <row r="14" spans="1:11" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="20"/>
-      <c r="B14" s="65">
+    </row>
+    <row r="28" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="28"/>
+      <c r="B28" s="21">
+        <v>3</v>
+      </c>
+      <c r="C28" s="201" t="s">
+        <v>122</v>
+      </c>
+      <c r="D28" s="202"/>
+      <c r="E28" s="202"/>
+      <c r="F28" s="203"/>
+      <c r="G28" s="94" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="28"/>
+      <c r="B29" s="21">
         <v>4</v>
       </c>
-      <c r="C14" s="191"/>
-      <c r="D14" s="192"/>
-      <c r="E14" s="192"/>
-      <c r="F14" s="193"/>
-    </row>
-    <row r="15" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="B15" s="67" t="s">
-        <v>52</v>
-      </c>
-      <c r="C15" s="188" t="s">
-        <v>53</v>
-      </c>
-      <c r="D15" s="189"/>
-      <c r="E15" s="189"/>
-      <c r="F15" s="190"/>
-      <c r="K15" s="53"/>
-    </row>
-    <row r="16" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="18"/>
-      <c r="B16" s="19">
+      <c r="C29" s="101" t="s">
+        <v>81</v>
+      </c>
+      <c r="D29" s="102"/>
+      <c r="E29" s="102"/>
+      <c r="F29" s="103"/>
+      <c r="G29" s="94" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="50"/>
+      <c r="B30" s="23">
+        <v>5</v>
+      </c>
+      <c r="C30" s="101" t="s">
+        <v>82</v>
+      </c>
+      <c r="D30" s="102"/>
+      <c r="E30" s="102"/>
+      <c r="F30" s="103"/>
+      <c r="G30" s="90" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A31" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="18">
+        <v>3</v>
+      </c>
+      <c r="C31" s="104" t="s">
+        <v>126</v>
+      </c>
+      <c r="D31" s="105"/>
+      <c r="E31" s="105"/>
+      <c r="F31" s="106"/>
+      <c r="G31" s="93" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A32" s="31"/>
+      <c r="B32" s="21">
         <v>4</v>
       </c>
-      <c r="C16" s="95" t="s">
-        <v>85</v>
-      </c>
-      <c r="D16" s="96"/>
-      <c r="E16" s="96"/>
-      <c r="F16" s="97"/>
-    </row>
-    <row r="17" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="18"/>
-      <c r="B17" s="19">
+      <c r="C32" s="119" t="s">
+        <v>127</v>
+      </c>
+      <c r="D32" s="120"/>
+      <c r="E32" s="120"/>
+      <c r="F32" s="121"/>
+      <c r="G32" s="94" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="32"/>
+      <c r="B33" s="23">
         <v>5</v>
       </c>
-      <c r="C17" s="95" t="s">
-        <v>86</v>
-      </c>
-      <c r="D17" s="96"/>
-      <c r="E17" s="96"/>
-      <c r="F17" s="97"/>
-    </row>
-    <row r="18" spans="1:6" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="24"/>
-      <c r="B18" s="21">
-        <v>6</v>
-      </c>
-      <c r="C18" s="126" t="s">
-        <v>123</v>
-      </c>
-      <c r="D18" s="127"/>
-      <c r="E18" s="127"/>
-      <c r="F18" s="128"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A19" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" s="17">
-        <v>1</v>
-      </c>
-      <c r="C19" s="178"/>
-      <c r="D19" s="179"/>
-      <c r="E19" s="179"/>
-      <c r="F19" s="180"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A20" s="18"/>
-      <c r="B20" s="19">
-        <v>2</v>
-      </c>
-      <c r="C20" s="152" t="s">
-        <v>94</v>
-      </c>
-      <c r="D20" s="153"/>
-      <c r="E20" s="153"/>
-      <c r="F20" s="154"/>
-    </row>
-    <row r="21" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="18"/>
-      <c r="B21" s="19">
-        <v>3</v>
-      </c>
-      <c r="C21" s="152" t="s">
-        <v>95</v>
-      </c>
-      <c r="D21" s="153"/>
-      <c r="E21" s="153"/>
-      <c r="F21" s="154"/>
-    </row>
-    <row r="22" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="24"/>
-      <c r="B22" s="21">
-        <v>4</v>
-      </c>
-      <c r="C22" s="194"/>
-      <c r="D22" s="195"/>
-      <c r="E22" s="195"/>
-      <c r="F22" s="196"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A23" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="B23" s="17">
-        <v>2</v>
-      </c>
-      <c r="C23" s="197"/>
-      <c r="D23" s="198"/>
-      <c r="E23" s="198"/>
-      <c r="F23" s="199"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A24" s="18"/>
-      <c r="B24" s="19">
-        <v>3</v>
-      </c>
-      <c r="C24" s="181" t="s">
-        <v>96</v>
-      </c>
-      <c r="D24" s="182"/>
-      <c r="E24" s="182"/>
-      <c r="F24" s="183"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A25" s="18"/>
-      <c r="B25" s="19">
-        <v>4</v>
-      </c>
-      <c r="C25" s="181" t="s">
-        <v>97</v>
-      </c>
-      <c r="D25" s="182"/>
-      <c r="E25" s="182"/>
-      <c r="F25" s="183"/>
-    </row>
-    <row r="26" spans="1:6" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="24"/>
-      <c r="B26" s="21">
-        <v>5</v>
-      </c>
-      <c r="C26" s="191"/>
-      <c r="D26" s="192"/>
-      <c r="E26" s="200" t="s">
-        <v>84</v>
-      </c>
-      <c r="F26" s="201"/>
-    </row>
-    <row r="27" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="B27" s="17">
-        <v>2</v>
-      </c>
-      <c r="C27" s="178" t="s">
-        <v>87</v>
-      </c>
-      <c r="D27" s="179"/>
-      <c r="E27" s="179"/>
-      <c r="F27" s="180"/>
-    </row>
-    <row r="28" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="25"/>
-      <c r="B28" s="19">
-        <v>3</v>
-      </c>
-      <c r="C28" s="181" t="s">
-        <v>88</v>
-      </c>
-      <c r="D28" s="182"/>
-      <c r="E28" s="182"/>
-      <c r="F28" s="183"/>
-    </row>
-    <row r="29" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="25"/>
-      <c r="B29" s="19">
-        <v>4</v>
-      </c>
-      <c r="C29" s="80" t="s">
-        <v>57</v>
-      </c>
-      <c r="D29" s="81"/>
-      <c r="E29" s="81"/>
-      <c r="F29" s="82"/>
-    </row>
-    <row r="30" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="46"/>
-      <c r="B30" s="21">
-        <v>5</v>
-      </c>
-      <c r="C30" s="80" t="s">
-        <v>58</v>
-      </c>
-      <c r="D30" s="81"/>
-      <c r="E30" s="81"/>
-      <c r="F30" s="82"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A31" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="B31" s="17">
-        <v>3</v>
-      </c>
-      <c r="C31" s="123" t="s">
-        <v>92</v>
-      </c>
-      <c r="D31" s="124"/>
-      <c r="E31" s="124"/>
-      <c r="F31" s="125"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A32" s="28"/>
-      <c r="B32" s="19">
-        <v>4</v>
-      </c>
-      <c r="C32" s="116" t="s">
-        <v>93</v>
-      </c>
-      <c r="D32" s="117"/>
-      <c r="E32" s="117"/>
-      <c r="F32" s="118"/>
-    </row>
-    <row r="33" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="29"/>
-      <c r="B33" s="21">
-        <v>5</v>
-      </c>
-      <c r="C33" s="169"/>
-      <c r="D33" s="170"/>
-      <c r="E33" s="170"/>
-      <c r="F33" s="171"/>
-    </row>
-    <row r="34" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="63"/>
-      <c r="B34" s="64"/>
-      <c r="C34" s="172"/>
-      <c r="D34" s="173"/>
-      <c r="E34" s="173"/>
-      <c r="F34" s="174"/>
-    </row>
-    <row r="35" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="70"/>
-      <c r="B35" s="71" t="s">
-        <v>32</v>
-      </c>
-      <c r="C35" s="175" t="s">
-        <v>56</v>
-      </c>
-      <c r="D35" s="176"/>
-      <c r="E35" s="176"/>
-      <c r="F35" s="177"/>
-    </row>
-    <row r="36" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="68" t="s">
-        <v>54</v>
-      </c>
-      <c r="B36" s="69"/>
-      <c r="C36" s="187" t="s">
-        <v>55</v>
-      </c>
-      <c r="D36" s="187"/>
-      <c r="E36" s="187"/>
-      <c r="F36" s="187"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="C33" s="218"/>
+      <c r="D33" s="219"/>
+      <c r="E33" s="219"/>
+      <c r="F33" s="220"/>
+      <c r="G33" s="90"/>
+    </row>
+    <row r="34" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="68"/>
+      <c r="B34" s="69"/>
+      <c r="C34" s="221"/>
+      <c r="D34" s="222"/>
+      <c r="E34" s="222"/>
+      <c r="F34" s="223"/>
+      <c r="G34" s="70"/>
+    </row>
+    <row r="35" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="79"/>
+      <c r="B35" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="C35" s="224" t="s">
+        <v>77</v>
+      </c>
+      <c r="D35" s="225"/>
+      <c r="E35" s="225"/>
+      <c r="F35" s="226"/>
+      <c r="G35" s="95" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="44.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="77" t="s">
+        <v>74</v>
+      </c>
+      <c r="B36" s="78"/>
+      <c r="C36" s="197" t="s">
+        <v>75</v>
+      </c>
+      <c r="D36" s="197"/>
+      <c r="E36" s="197"/>
+      <c r="F36" s="197"/>
+      <c r="G36" s="57"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A37" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A38" s="2" t="s">
         <v>15</v>
       </c>
@@ -3815,19 +4226,6 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C32:F32"/>
     <mergeCell ref="C33:F33"/>
@@ -3844,6 +4242,19 @@
     <mergeCell ref="C18:F18"/>
     <mergeCell ref="C19:F19"/>
     <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C6"/>
@@ -3895,7 +4306,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -3904,10 +4315,11 @@
     <col min="4" max="4" width="19.140625" style="2" customWidth="1"/>
     <col min="5" max="5" width="20.140625" style="2" customWidth="1"/>
     <col min="6" max="6" width="18.85546875" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -3915,15 +4327,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -3931,95 +4343,95 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
-      <c r="F4" s="72" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A5" s="54" t="s">
+      <c r="F4" s="86" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A5" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="61"/>
-      <c r="C5" s="56" t="s">
-        <v>65</v>
-      </c>
-      <c r="D5" s="56"/>
-      <c r="E5" s="57" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5" s="59" t="s">
+      <c r="B5" s="65"/>
+      <c r="C5" s="60" t="s">
+        <v>90</v>
+      </c>
+      <c r="D5" s="60"/>
+      <c r="E5" s="61" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="63" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="55" t="s">
+    <row r="6" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="61"/>
-      <c r="C6" s="51" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="51"/>
-      <c r="E6" s="57">
+      <c r="B6" s="65"/>
+      <c r="C6" s="55" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="55"/>
+      <c r="E6" s="61">
         <v>4</v>
       </c>
-      <c r="F6" s="59" t="s">
+      <c r="F6" s="63" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="55" t="s">
+    <row r="7" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="59" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="65"/>
+      <c r="C7" s="54" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="54"/>
+      <c r="E7" s="62" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="64" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="59" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="65"/>
+      <c r="C8" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="61"/>
-      <c r="C7" s="50" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="50"/>
-      <c r="E7" s="58" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7" s="60" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="55" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="61"/>
-      <c r="C8" s="51" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="51"/>
-    </row>
-    <row r="9" spans="1:6" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="55" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" s="61"/>
-      <c r="C9" s="73" t="s">
-        <v>66</v>
-      </c>
-      <c r="D9" s="73"/>
-      <c r="E9" s="52"/>
-      <c r="F9" s="51"/>
-    </row>
-    <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" s="39" t="s">
+      <c r="D8" s="56"/>
+      <c r="E8" s="56"/>
+      <c r="F8" s="55"/>
+    </row>
+    <row r="9" spans="1:7" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="59" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="65"/>
+      <c r="C9" s="135" t="s">
+        <v>91</v>
+      </c>
+      <c r="D9" s="135"/>
+      <c r="E9" s="56"/>
+      <c r="F9" s="55"/>
+    </row>
+    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="43" t="s">
         <v>0</v>
       </c>
       <c r="C10" s="12" t="s">
@@ -4028,308 +4440,364 @@
       <c r="D10" s="13"/>
       <c r="E10" s="14"/>
       <c r="F10" s="15"/>
-    </row>
-    <row r="11" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="44" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="45">
+      <c r="G10" s="16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="48" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="49">
         <v>2</v>
       </c>
-      <c r="C11" s="229" t="s">
-        <v>99</v>
-      </c>
-      <c r="D11" s="230"/>
-      <c r="E11" s="230" t="s">
-        <v>122</v>
-      </c>
-      <c r="F11" s="231"/>
-    </row>
-    <row r="12" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="18"/>
-      <c r="B12" s="19">
+      <c r="C11" s="248" t="s">
+        <v>135</v>
+      </c>
+      <c r="D11" s="249"/>
+      <c r="E11" s="249" t="s">
+        <v>160</v>
+      </c>
+      <c r="F11" s="250"/>
+      <c r="G11" s="91" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="20"/>
+      <c r="B12" s="21">
         <v>3</v>
       </c>
-      <c r="C12" s="107" t="s">
-        <v>98</v>
-      </c>
-      <c r="D12" s="108"/>
-      <c r="E12" s="108"/>
-      <c r="F12" s="109"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A13" s="18"/>
-      <c r="B13" s="19">
+      <c r="C12" s="129" t="s">
+        <v>132</v>
+      </c>
+      <c r="D12" s="130"/>
+      <c r="E12" s="130"/>
+      <c r="F12" s="131"/>
+      <c r="G12" s="88" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A13" s="20"/>
+      <c r="B13" s="21">
         <v>4</v>
       </c>
-      <c r="C13" s="107" t="s">
-        <v>60</v>
-      </c>
-      <c r="D13" s="108"/>
-      <c r="E13" s="108"/>
-      <c r="F13" s="109"/>
-    </row>
-    <row r="14" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="20"/>
-      <c r="B14" s="21">
+      <c r="C13" s="129" t="s">
+        <v>85</v>
+      </c>
+      <c r="D13" s="130"/>
+      <c r="E13" s="130"/>
+      <c r="F13" s="131"/>
+      <c r="G13" s="88" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="22"/>
+      <c r="B14" s="23">
         <v>5</v>
       </c>
-      <c r="C14" s="226" t="s">
-        <v>100</v>
-      </c>
-      <c r="D14" s="227"/>
-      <c r="E14" s="227"/>
-      <c r="F14" s="228"/>
-    </row>
-    <row r="15" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="B15" s="17">
+      <c r="C14" s="245" t="s">
+        <v>136</v>
+      </c>
+      <c r="D14" s="246"/>
+      <c r="E14" s="246"/>
+      <c r="F14" s="247"/>
+      <c r="G14" s="92" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="18">
         <v>1</v>
       </c>
-      <c r="C15" s="202"/>
-      <c r="D15" s="203"/>
-      <c r="E15" s="203"/>
-      <c r="F15" s="204"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A16" s="18"/>
-      <c r="B16" s="19">
+      <c r="C15" s="251"/>
+      <c r="D15" s="252"/>
+      <c r="E15" s="252"/>
+      <c r="F15" s="253"/>
+      <c r="G15" s="19"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A16" s="20"/>
+      <c r="B16" s="21">
         <v>2</v>
       </c>
-      <c r="C16" s="217"/>
-      <c r="D16" s="218"/>
-      <c r="E16" s="218"/>
-      <c r="F16" s="219"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A17" s="18"/>
-      <c r="B17" s="19">
+      <c r="C16" s="233"/>
+      <c r="D16" s="234"/>
+      <c r="E16" s="234"/>
+      <c r="F16" s="235"/>
+      <c r="G16" s="94"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A17" s="20"/>
+      <c r="B17" s="21">
         <v>3</v>
       </c>
-      <c r="C17" s="220"/>
-      <c r="D17" s="221"/>
-      <c r="E17" s="221"/>
-      <c r="F17" s="222"/>
-    </row>
-    <row r="18" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="18"/>
-      <c r="B18" s="19">
+      <c r="C17" s="236"/>
+      <c r="D17" s="237"/>
+      <c r="E17" s="237"/>
+      <c r="F17" s="238"/>
+      <c r="G17" s="88"/>
+    </row>
+    <row r="18" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="20"/>
+      <c r="B18" s="21">
         <v>4</v>
       </c>
-      <c r="C18" s="214" t="s">
-        <v>101</v>
-      </c>
-      <c r="D18" s="215"/>
-      <c r="E18" s="215"/>
-      <c r="F18" s="216"/>
-    </row>
-    <row r="19" spans="1:6" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="24"/>
-      <c r="B19" s="21">
+      <c r="C18" s="230" t="s">
+        <v>137</v>
+      </c>
+      <c r="D18" s="231"/>
+      <c r="E18" s="231"/>
+      <c r="F18" s="232"/>
+      <c r="G18" s="94" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="27"/>
+      <c r="B19" s="23">
         <v>5</v>
       </c>
-      <c r="C19" s="194"/>
-      <c r="D19" s="195"/>
-      <c r="E19" s="195"/>
-      <c r="F19" s="196"/>
-    </row>
-    <row r="20" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20" s="17">
+      <c r="C19" s="210"/>
+      <c r="D19" s="211"/>
+      <c r="E19" s="211"/>
+      <c r="F19" s="212"/>
+      <c r="G19" s="90"/>
+    </row>
+    <row r="20" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="18">
         <v>3</v>
       </c>
-      <c r="C20" s="77" t="s">
-        <v>102</v>
-      </c>
-      <c r="D20" s="78"/>
-      <c r="E20" s="78"/>
-      <c r="F20" s="79"/>
-    </row>
-    <row r="21" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="18"/>
-      <c r="B21" s="19">
+      <c r="C20" s="132" t="s">
+        <v>138</v>
+      </c>
+      <c r="D20" s="133"/>
+      <c r="E20" s="133"/>
+      <c r="F20" s="134"/>
+      <c r="G20" s="91" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="20"/>
+      <c r="B21" s="21">
         <v>4</v>
       </c>
-      <c r="C21" s="107" t="s">
-        <v>103</v>
-      </c>
-      <c r="D21" s="108"/>
-      <c r="E21" s="108"/>
-      <c r="F21" s="109"/>
-    </row>
-    <row r="22" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="18"/>
-      <c r="B22" s="19">
+      <c r="C21" s="129" t="s">
+        <v>139</v>
+      </c>
+      <c r="D21" s="130"/>
+      <c r="E21" s="130"/>
+      <c r="F21" s="131"/>
+      <c r="G21" s="88" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="20"/>
+      <c r="B22" s="21">
         <v>5</v>
       </c>
-      <c r="C22" s="107" t="s">
-        <v>104</v>
-      </c>
-      <c r="D22" s="108"/>
-      <c r="E22" s="108"/>
-      <c r="F22" s="109"/>
-    </row>
-    <row r="23" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="24"/>
-      <c r="B23" s="21">
+      <c r="C22" s="129" t="s">
+        <v>140</v>
+      </c>
+      <c r="D22" s="130"/>
+      <c r="E22" s="130"/>
+      <c r="F22" s="131"/>
+      <c r="G22" s="88" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="27"/>
+      <c r="B23" s="23">
         <v>6</v>
       </c>
-      <c r="C23" s="160"/>
-      <c r="D23" s="161"/>
-      <c r="E23" s="161"/>
-      <c r="F23" s="162"/>
-    </row>
-    <row r="24" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="B24" s="17">
+      <c r="C23" s="166"/>
+      <c r="D23" s="167"/>
+      <c r="E23" s="167"/>
+      <c r="F23" s="168"/>
+      <c r="G23" s="82"/>
+    </row>
+    <row r="24" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" s="18">
         <v>1</v>
       </c>
-      <c r="C24" s="211"/>
-      <c r="D24" s="212"/>
-      <c r="E24" s="212"/>
-      <c r="F24" s="213"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A25" s="18"/>
-      <c r="B25" s="19">
+      <c r="C24" s="239"/>
+      <c r="D24" s="240"/>
+      <c r="E24" s="240"/>
+      <c r="F24" s="241"/>
+      <c r="G24" s="91"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A25" s="20"/>
+      <c r="B25" s="21">
         <v>2</v>
       </c>
-      <c r="C25" s="223"/>
-      <c r="D25" s="224"/>
-      <c r="E25" s="224"/>
-      <c r="F25" s="225"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A26" s="18"/>
-      <c r="B26" s="19">
+      <c r="C25" s="242"/>
+      <c r="D25" s="243"/>
+      <c r="E25" s="243"/>
+      <c r="F25" s="244"/>
+      <c r="G25" s="88"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A26" s="20"/>
+      <c r="B26" s="21">
         <v>3</v>
       </c>
-      <c r="C26" s="214" t="s">
-        <v>120</v>
-      </c>
-      <c r="D26" s="215"/>
-      <c r="E26" s="215"/>
-      <c r="F26" s="216"/>
-    </row>
-    <row r="27" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="24"/>
-      <c r="B27" s="21">
+      <c r="C26" s="230" t="s">
+        <v>158</v>
+      </c>
+      <c r="D26" s="231"/>
+      <c r="E26" s="231"/>
+      <c r="F26" s="232"/>
+      <c r="G26" s="94" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A27" s="27"/>
+      <c r="B27" s="23">
         <v>4</v>
       </c>
-      <c r="C27" s="205" t="s">
-        <v>121</v>
-      </c>
-      <c r="D27" s="206"/>
-      <c r="E27" s="206"/>
-      <c r="F27" s="207"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A28" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="B28" s="17">
+      <c r="C27" s="254" t="s">
+        <v>159</v>
+      </c>
+      <c r="D27" s="255"/>
+      <c r="E27" s="255"/>
+      <c r="F27" s="256"/>
+      <c r="G27" s="99" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A28" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" s="18">
         <v>2</v>
       </c>
-      <c r="C28" s="178" t="s">
-        <v>105</v>
-      </c>
-      <c r="D28" s="179"/>
-      <c r="E28" s="179"/>
-      <c r="F28" s="180"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A29" s="25"/>
-      <c r="B29" s="19">
+      <c r="C28" s="227" t="s">
+        <v>141</v>
+      </c>
+      <c r="D28" s="228"/>
+      <c r="E28" s="228"/>
+      <c r="F28" s="229"/>
+      <c r="G28" s="91" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A29" s="28"/>
+      <c r="B29" s="21">
         <v>3</v>
       </c>
-      <c r="C29" s="107" t="s">
-        <v>106</v>
-      </c>
-      <c r="D29" s="108"/>
-      <c r="E29" s="108"/>
-      <c r="F29" s="109"/>
-    </row>
-    <row r="30" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="25"/>
-      <c r="B30" s="19">
+      <c r="C29" s="129" t="s">
+        <v>142</v>
+      </c>
+      <c r="D29" s="130"/>
+      <c r="E29" s="130"/>
+      <c r="F29" s="131"/>
+      <c r="G29" s="88" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="28"/>
+      <c r="B30" s="21">
         <v>4</v>
       </c>
-      <c r="C30" s="208"/>
-      <c r="D30" s="209"/>
-      <c r="E30" s="209"/>
-      <c r="F30" s="210"/>
-    </row>
-    <row r="31" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="46"/>
-      <c r="B31" s="21">
+      <c r="C30" s="257"/>
+      <c r="D30" s="258"/>
+      <c r="E30" s="258"/>
+      <c r="F30" s="259"/>
+      <c r="G30" s="84"/>
+    </row>
+    <row r="31" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="50"/>
+      <c r="B31" s="23">
         <v>5</v>
       </c>
-      <c r="C31" s="129"/>
-      <c r="D31" s="130"/>
-      <c r="E31" s="130"/>
-      <c r="F31" s="131"/>
-    </row>
-    <row r="32" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="47" t="s">
-        <v>28</v>
-      </c>
-      <c r="B32" s="45">
+      <c r="C31" s="110"/>
+      <c r="D31" s="111"/>
+      <c r="E31" s="111"/>
+      <c r="F31" s="112"/>
+      <c r="G31" s="82"/>
+    </row>
+    <row r="32" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="B32" s="49">
         <v>2</v>
       </c>
-      <c r="C32" s="211" t="s">
-        <v>107</v>
-      </c>
-      <c r="D32" s="212"/>
-      <c r="E32" s="212"/>
-      <c r="F32" s="213"/>
-    </row>
-    <row r="33" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="28"/>
-      <c r="B33" s="19">
+      <c r="C32" s="239" t="s">
+        <v>143</v>
+      </c>
+      <c r="D32" s="240"/>
+      <c r="E32" s="240"/>
+      <c r="F32" s="241"/>
+      <c r="G32" s="96" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="31"/>
+      <c r="B33" s="21">
         <v>3</v>
       </c>
-      <c r="C33" s="80" t="s">
-        <v>108</v>
-      </c>
-      <c r="D33" s="81"/>
-      <c r="E33" s="81"/>
-      <c r="F33" s="82"/>
-    </row>
-    <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="28"/>
-      <c r="B34" s="19">
+      <c r="C33" s="101" t="s">
+        <v>144</v>
+      </c>
+      <c r="D33" s="102"/>
+      <c r="E33" s="102"/>
+      <c r="F33" s="103"/>
+      <c r="G33" s="94" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="31"/>
+      <c r="B34" s="21">
         <v>4</v>
       </c>
-      <c r="C34" s="132"/>
-      <c r="D34" s="133"/>
-      <c r="E34" s="133"/>
-      <c r="F34" s="134"/>
-    </row>
-    <row r="35" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="48"/>
-      <c r="B35" s="49">
+      <c r="C34" s="113"/>
+      <c r="D34" s="114"/>
+      <c r="E34" s="114"/>
+      <c r="F34" s="115"/>
+      <c r="G34" s="39"/>
+    </row>
+    <row r="35" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="52"/>
+      <c r="B35" s="53">
         <v>5</v>
       </c>
-      <c r="C35" s="158"/>
-      <c r="D35" s="159"/>
-      <c r="E35" s="159"/>
-      <c r="F35" s="140"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="C35" s="163"/>
+      <c r="D35" s="164"/>
+      <c r="E35" s="164"/>
+      <c r="F35" s="165"/>
+      <c r="G35" s="24"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A37" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A38" s="2" t="s">
         <v>15</v>
       </c>
@@ -4339,6 +4807,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C32:F32"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C26:F26"/>
     <mergeCell ref="C16:F16"/>
@@ -4355,17 +4834,6 @@
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C32:F32"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5">
@@ -4417,7 +4885,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -4426,10 +4894,11 @@
     <col min="4" max="4" width="17.85546875" style="2" customWidth="1"/>
     <col min="5" max="5" width="16.140625" style="2" customWidth="1"/>
     <col min="6" max="6" width="17.5703125" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -4437,15 +4906,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -4453,389 +4922,429 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
-      <c r="F4" s="72" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A5" s="54" t="s">
+      <c r="F4" s="86" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A5" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="61"/>
-      <c r="C5" s="56" t="s">
-        <v>65</v>
-      </c>
-      <c r="D5" s="56"/>
-      <c r="E5" s="57" t="s">
+      <c r="B5" s="65"/>
+      <c r="C5" s="60" t="s">
+        <v>90</v>
+      </c>
+      <c r="D5" s="60"/>
+      <c r="E5" s="61" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="63" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="59" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="65"/>
+      <c r="C6" s="55" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="55"/>
+      <c r="E6" s="61">
+        <v>5</v>
+      </c>
+      <c r="F6" s="63" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="59" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="65"/>
+      <c r="C7" s="54" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="54"/>
+      <c r="E7" s="62" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="64" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="59" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="65"/>
+      <c r="C8" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="56"/>
+      <c r="E8" s="56"/>
+      <c r="F8" s="55"/>
+    </row>
+    <row r="9" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="59" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="65"/>
+      <c r="C9" s="135" t="s">
+        <v>92</v>
+      </c>
+      <c r="D9" s="135"/>
+      <c r="E9" s="56"/>
+      <c r="F9" s="55"/>
+    </row>
+    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="43" t="s">
+        <v>0</v>
+      </c>
+      <c r="C10" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" s="45"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="47"/>
+      <c r="G10" s="16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A11" s="48" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="49">
+        <v>1</v>
+      </c>
+      <c r="C11" s="189"/>
+      <c r="D11" s="190"/>
+      <c r="E11" s="190"/>
+      <c r="F11" s="191"/>
+      <c r="G11" s="19"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A12" s="20"/>
+      <c r="B12" s="21">
+        <v>2</v>
+      </c>
+      <c r="C12" s="101" t="s">
+        <v>146</v>
+      </c>
+      <c r="D12" s="102"/>
+      <c r="E12" s="102"/>
+      <c r="F12" s="103"/>
+      <c r="G12" s="94" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A13" s="20"/>
+      <c r="B13" s="21">
+        <v>3</v>
+      </c>
+      <c r="C13" s="119" t="s">
+        <v>147</v>
+      </c>
+      <c r="D13" s="120"/>
+      <c r="E13" s="120"/>
+      <c r="F13" s="121"/>
+      <c r="G13" s="94" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="22"/>
+      <c r="B14" s="23">
+        <v>4</v>
+      </c>
+      <c r="C14" s="172"/>
+      <c r="D14" s="173"/>
+      <c r="E14" s="173"/>
+      <c r="F14" s="174"/>
+      <c r="G14" s="90"/>
+    </row>
+    <row r="15" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="18">
+        <v>3</v>
+      </c>
+      <c r="C15" s="266" t="s">
         <v>34</v>
       </c>
-      <c r="F5" s="59" t="s">
+      <c r="D15" s="267"/>
+      <c r="E15" s="267"/>
+      <c r="F15" s="268"/>
+      <c r="G15" s="19"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A16" s="20"/>
+      <c r="B16" s="21">
+        <v>4</v>
+      </c>
+      <c r="C16" s="113"/>
+      <c r="D16" s="114"/>
+      <c r="E16" s="114"/>
+      <c r="F16" s="115"/>
+      <c r="G16" s="94"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A17" s="20"/>
+      <c r="B17" s="21">
+        <v>5</v>
+      </c>
+      <c r="C17" s="113"/>
+      <c r="D17" s="114"/>
+      <c r="E17" s="114"/>
+      <c r="F17" s="115"/>
+      <c r="G17" s="94"/>
+    </row>
+    <row r="18" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="27"/>
+      <c r="B18" s="23">
+        <v>6</v>
+      </c>
+      <c r="C18" s="163"/>
+      <c r="D18" s="164"/>
+      <c r="E18" s="164"/>
+      <c r="F18" s="165"/>
+      <c r="G18" s="39"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A19" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="18">
+        <v>2</v>
+      </c>
+      <c r="C19" s="136"/>
+      <c r="D19" s="137"/>
+      <c r="E19" s="137"/>
+      <c r="F19" s="138"/>
+      <c r="G19" s="93"/>
+    </row>
+    <row r="20" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="20"/>
+      <c r="B20" s="21">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="55" t="s">
+      <c r="C20" s="113"/>
+      <c r="D20" s="114"/>
+      <c r="E20" s="114"/>
+      <c r="F20" s="115"/>
+      <c r="G20" s="94"/>
+    </row>
+    <row r="21" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="20"/>
+      <c r="B21" s="21">
         <v>4</v>
       </c>
-      <c r="B6" s="61"/>
-      <c r="C6" s="51" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="51"/>
-      <c r="E6" s="57">
+      <c r="C21" s="101" t="s">
+        <v>152</v>
+      </c>
+      <c r="D21" s="102"/>
+      <c r="E21" s="102"/>
+      <c r="F21" s="103"/>
+      <c r="G21" s="94" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="27"/>
+      <c r="B22" s="23">
         <v>5</v>
       </c>
-      <c r="F6" s="59" t="s">
+      <c r="C22" s="172" t="s">
+        <v>153</v>
+      </c>
+      <c r="D22" s="173"/>
+      <c r="E22" s="173"/>
+      <c r="F22" s="174"/>
+      <c r="G22" s="90" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A23" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" s="18">
+        <v>2</v>
+      </c>
+      <c r="C23" s="263"/>
+      <c r="D23" s="264"/>
+      <c r="E23" s="264"/>
+      <c r="F23" s="265"/>
+      <c r="G23" s="19"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A24" s="20"/>
+      <c r="B24" s="21">
+        <v>3</v>
+      </c>
+      <c r="C24" s="260"/>
+      <c r="D24" s="261"/>
+      <c r="E24" s="261"/>
+      <c r="F24" s="262"/>
+      <c r="G24" s="39"/>
+    </row>
+    <row r="25" spans="1:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="20"/>
+      <c r="B25" s="21">
+        <v>4</v>
+      </c>
+      <c r="C25" s="101" t="s">
+        <v>148</v>
+      </c>
+      <c r="D25" s="102"/>
+      <c r="E25" s="102"/>
+      <c r="F25" s="103"/>
+      <c r="G25" s="94" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="27"/>
+      <c r="B26" s="23">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="55" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="61"/>
-      <c r="C7" s="50" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="50"/>
-      <c r="E7" s="58" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" s="60" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="55" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="61"/>
-      <c r="C8" s="51" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="51"/>
-    </row>
-    <row r="9" spans="1:6" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="55" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" s="61"/>
-      <c r="C9" s="73" t="s">
-        <v>67</v>
-      </c>
-      <c r="D9" s="73"/>
-      <c r="E9" s="52"/>
-      <c r="F9" s="51"/>
-    </row>
-    <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" s="39" t="s">
-        <v>0</v>
-      </c>
-      <c r="C10" s="40" t="s">
+      <c r="C26" s="172" t="s">
+        <v>149</v>
+      </c>
+      <c r="D26" s="173"/>
+      <c r="E26" s="173"/>
+      <c r="F26" s="174"/>
+      <c r="G26" s="90" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A27" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" s="18">
+        <v>2</v>
+      </c>
+      <c r="C27" s="266" t="s">
+        <v>34</v>
+      </c>
+      <c r="D27" s="267"/>
+      <c r="E27" s="267"/>
+      <c r="F27" s="268"/>
+      <c r="G27" s="19"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A28" s="28"/>
+      <c r="B28" s="21">
+        <v>3</v>
+      </c>
+      <c r="C28" s="269"/>
+      <c r="D28" s="270"/>
+      <c r="E28" s="270"/>
+      <c r="F28" s="271"/>
+      <c r="G28" s="39"/>
+    </row>
+    <row r="29" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="28"/>
+      <c r="B29" s="21">
+        <v>4</v>
+      </c>
+      <c r="C29" s="113"/>
+      <c r="D29" s="114"/>
+      <c r="E29" s="114"/>
+      <c r="F29" s="115"/>
+      <c r="G29" s="39"/>
+    </row>
+    <row r="30" spans="1:7" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="50"/>
+      <c r="B30" s="23">
+        <v>5</v>
+      </c>
+      <c r="C30" s="272"/>
+      <c r="D30" s="273"/>
+      <c r="E30" s="273"/>
+      <c r="F30" s="274"/>
+      <c r="G30" s="73"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A31" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="49">
         <v>1</v>
       </c>
-      <c r="D10" s="41"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="43"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A11" s="44" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="45">
-        <v>1</v>
-      </c>
-      <c r="C11" s="155"/>
-      <c r="D11" s="156"/>
-      <c r="E11" s="156"/>
-      <c r="F11" s="157"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A12" s="18"/>
-      <c r="B12" s="19">
+      <c r="C31" s="266" t="s">
+        <v>34</v>
+      </c>
+      <c r="D31" s="267"/>
+      <c r="E31" s="267"/>
+      <c r="F31" s="268"/>
+      <c r="G31" s="19"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A32" s="31"/>
+      <c r="B32" s="21">
         <v>2</v>
       </c>
-      <c r="C12" s="80" t="s">
-        <v>109</v>
-      </c>
-      <c r="D12" s="81"/>
-      <c r="E12" s="81"/>
-      <c r="F12" s="82"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A13" s="18"/>
-      <c r="B13" s="19">
+      <c r="C32" s="260"/>
+      <c r="D32" s="261"/>
+      <c r="E32" s="261"/>
+      <c r="F32" s="262"/>
+      <c r="G32" s="39"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A33" s="31"/>
+      <c r="B33" s="21">
         <v>3</v>
       </c>
-      <c r="C13" s="116" t="s">
-        <v>110</v>
-      </c>
-      <c r="D13" s="117"/>
-      <c r="E13" s="117"/>
-      <c r="F13" s="118"/>
-    </row>
-    <row r="14" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="20"/>
-      <c r="B14" s="21">
-        <v>4</v>
-      </c>
-      <c r="C14" s="163"/>
-      <c r="D14" s="164"/>
-      <c r="E14" s="164"/>
-      <c r="F14" s="165"/>
-    </row>
-    <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="B15" s="17">
-        <v>3</v>
-      </c>
-      <c r="C15" s="235" t="s">
-        <v>33</v>
-      </c>
-      <c r="D15" s="236"/>
-      <c r="E15" s="236"/>
-      <c r="F15" s="237"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A16" s="18"/>
-      <c r="B16" s="19">
-        <v>4</v>
-      </c>
-      <c r="C16" s="132"/>
-      <c r="D16" s="133"/>
-      <c r="E16" s="133"/>
-      <c r="F16" s="134"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A17" s="18"/>
-      <c r="B17" s="19">
-        <v>5</v>
-      </c>
-      <c r="C17" s="132"/>
-      <c r="D17" s="133"/>
-      <c r="E17" s="133"/>
-      <c r="F17" s="134"/>
-    </row>
-    <row r="18" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="24"/>
-      <c r="B18" s="21">
-        <v>6</v>
-      </c>
-      <c r="C18" s="158"/>
-      <c r="D18" s="159"/>
-      <c r="E18" s="159"/>
-      <c r="F18" s="140"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A19" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" s="17">
-        <v>2</v>
-      </c>
-      <c r="C19" s="74"/>
-      <c r="D19" s="75"/>
-      <c r="E19" s="75"/>
-      <c r="F19" s="76"/>
-    </row>
-    <row r="20" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="18"/>
-      <c r="B20" s="19">
-        <v>3</v>
-      </c>
-      <c r="C20" s="132"/>
-      <c r="D20" s="133"/>
-      <c r="E20" s="133"/>
-      <c r="F20" s="134"/>
-    </row>
-    <row r="21" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="18"/>
-      <c r="B21" s="19">
-        <v>4</v>
-      </c>
-      <c r="C21" s="80" t="s">
-        <v>115</v>
-      </c>
-      <c r="D21" s="81"/>
-      <c r="E21" s="81"/>
-      <c r="F21" s="82"/>
-    </row>
-    <row r="22" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="24"/>
-      <c r="B22" s="21">
-        <v>5</v>
-      </c>
-      <c r="C22" s="163" t="s">
-        <v>116</v>
-      </c>
-      <c r="D22" s="164"/>
-      <c r="E22" s="164"/>
-      <c r="F22" s="165"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A23" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="B23" s="17">
-        <v>2</v>
-      </c>
-      <c r="C23" s="244"/>
-      <c r="D23" s="245"/>
-      <c r="E23" s="245"/>
-      <c r="F23" s="246"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A24" s="18"/>
-      <c r="B24" s="19">
-        <v>3</v>
-      </c>
-      <c r="C24" s="232"/>
-      <c r="D24" s="233"/>
-      <c r="E24" s="233"/>
-      <c r="F24" s="234"/>
-    </row>
-    <row r="25" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="18"/>
-      <c r="B25" s="19">
-        <v>4</v>
-      </c>
-      <c r="C25" s="80" t="s">
-        <v>111</v>
-      </c>
-      <c r="D25" s="81"/>
-      <c r="E25" s="81"/>
-      <c r="F25" s="82"/>
-    </row>
-    <row r="26" spans="1:6" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="24"/>
-      <c r="B26" s="21">
-        <v>5</v>
-      </c>
-      <c r="C26" s="163" t="s">
-        <v>112</v>
-      </c>
-      <c r="D26" s="164"/>
-      <c r="E26" s="164"/>
-      <c r="F26" s="165"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A27" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="B27" s="17">
-        <v>2</v>
-      </c>
-      <c r="C27" s="235" t="s">
-        <v>33</v>
-      </c>
-      <c r="D27" s="236"/>
-      <c r="E27" s="236"/>
-      <c r="F27" s="237"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A28" s="25"/>
-      <c r="B28" s="19">
-        <v>3</v>
-      </c>
-      <c r="C28" s="238"/>
-      <c r="D28" s="239"/>
-      <c r="E28" s="239"/>
-      <c r="F28" s="240"/>
-    </row>
-    <row r="29" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="25"/>
-      <c r="B29" s="19">
-        <v>4</v>
-      </c>
-      <c r="C29" s="132"/>
-      <c r="D29" s="133"/>
-      <c r="E29" s="133"/>
-      <c r="F29" s="134"/>
-    </row>
-    <row r="30" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="46"/>
-      <c r="B30" s="21">
-        <v>5</v>
-      </c>
-      <c r="C30" s="241"/>
-      <c r="D30" s="242"/>
-      <c r="E30" s="242"/>
-      <c r="F30" s="243"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A31" s="47" t="s">
-        <v>28</v>
-      </c>
-      <c r="B31" s="45">
-        <v>1</v>
-      </c>
-      <c r="C31" s="235" t="s">
-        <v>33</v>
-      </c>
-      <c r="D31" s="236"/>
-      <c r="E31" s="236"/>
-      <c r="F31" s="237"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A32" s="28"/>
-      <c r="B32" s="19">
-        <v>2</v>
-      </c>
-      <c r="C32" s="232"/>
-      <c r="D32" s="233"/>
-      <c r="E32" s="233"/>
-      <c r="F32" s="234"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A33" s="28"/>
-      <c r="B33" s="19">
-        <v>3</v>
-      </c>
-      <c r="C33" s="232"/>
-      <c r="D33" s="233"/>
-      <c r="E33" s="233"/>
-      <c r="F33" s="234"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A34" s="28"/>
-      <c r="B34" s="19"/>
-      <c r="C34" s="232"/>
-      <c r="D34" s="233"/>
-      <c r="E34" s="233"/>
-      <c r="F34" s="234"/>
-    </row>
-    <row r="35" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="48"/>
-      <c r="B35" s="49"/>
-      <c r="C35" s="158"/>
-      <c r="D35" s="159"/>
-      <c r="E35" s="159"/>
-      <c r="F35" s="140"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="C33" s="260"/>
+      <c r="D33" s="261"/>
+      <c r="E33" s="261"/>
+      <c r="F33" s="262"/>
+      <c r="G33" s="39"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A34" s="31"/>
+      <c r="B34" s="21"/>
+      <c r="C34" s="260"/>
+      <c r="D34" s="261"/>
+      <c r="E34" s="261"/>
+      <c r="F34" s="262"/>
+      <c r="G34" s="39"/>
+    </row>
+    <row r="35" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="52"/>
+      <c r="B35" s="53"/>
+      <c r="C35" s="163"/>
+      <c r="D35" s="164"/>
+      <c r="E35" s="164"/>
+      <c r="F35" s="165"/>
+      <c r="G35" s="24"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A37" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A38" s="2" t="s">
         <v>15</v>
       </c>
@@ -4845,6 +5354,16 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C33:F33"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C25:F25"/>
     <mergeCell ref="C24:F24"/>
@@ -4861,16 +5380,6 @@
     <mergeCell ref="C13:F13"/>
     <mergeCell ref="C14:F14"/>
     <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C33:F33"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C6"/>
